--- a/AAII_Financials/Quarterly/MNTK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MNTK_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="92">
   <si>
     <t>MNTK</t>
   </si>
@@ -656,88 +656,88 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43830</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43738</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
@@ -750,59 +750,62 @@
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>46800</v>
+      </c>
+      <c r="E8" s="3">
         <v>55700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>53300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>19200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>49600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>55900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>67900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>32200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>45300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>39700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>31700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>31400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>24800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>75600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>22000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>83700</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
@@ -815,59 +818,62 @@
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E9" s="3">
         <v>25700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>25400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>18100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>24700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>26300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>30000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>20400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>22400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>19800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>19200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>16800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>16100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>45700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>12200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>46500</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
@@ -880,59 +886,62 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E10" s="3">
         <v>30000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>27900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>24900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>29600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>37900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>11800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>22900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>19900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>12500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>14600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>8700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>29900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>9800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>37200</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
@@ -945,8 +954,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -970,8 +982,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1035,8 +1048,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1100,59 +1116,62 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>200</v>
+      </c>
+      <c r="E14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2300</v>
-      </c>
-      <c r="I14" s="3">
-        <v>100</v>
       </c>
       <c r="J14" s="3">
         <v>100</v>
       </c>
       <c r="K14" s="3">
+        <v>100</v>
+      </c>
+      <c r="L14" s="3">
         <v>700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>200</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>600</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1600</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1165,19 +1184,22 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="E15" s="3">
         <v>5300</v>
       </c>
       <c r="F15" s="3">
-        <v>5200</v>
+        <v>5300</v>
       </c>
       <c r="G15" s="3">
         <v>5200</v>
@@ -1186,16 +1208,16 @@
         <v>5200</v>
       </c>
       <c r="I15" s="3">
+        <v>5200</v>
+      </c>
+      <c r="J15" s="3">
         <v>5100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>5800</v>
-      </c>
-      <c r="L15" s="3">
-        <v>5700</v>
       </c>
       <c r="M15" s="3">
         <v>5700</v>
@@ -1204,20 +1226,20 @@
         <v>5700</v>
       </c>
       <c r="O15" s="3">
+        <v>5700</v>
+      </c>
+      <c r="P15" s="3">
         <v>6000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>16100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>5000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>14800</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1230,8 +1252,11 @@
       <c r="W15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1252,59 +1277,60 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E17" s="3">
         <v>38900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>39700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>33300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>41000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>42200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>43900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>33800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>36100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>33000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>32200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>43700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>26900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>69900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>21100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>73600</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1317,59 +1343,62 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E18" s="3">
         <v>16800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>13600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-14100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>8600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>13700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>24000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>6700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-12300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>5700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>10100</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1382,8 +1411,11 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1407,59 +1439,60 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-600</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1472,59 +1505,62 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E21" s="3">
         <v>22400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>18900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-9000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>13900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>18900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>29100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>15000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>11800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>5100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-6500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>21500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>25000</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1537,59 +1573,62 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E22" s="3">
         <v>1300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1500</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
       <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
         <v>300</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
       <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
         <v>900</v>
-      </c>
-      <c r="L22" s="3">
-        <v>700</v>
       </c>
       <c r="M22" s="3">
         <v>700</v>
       </c>
       <c r="N22" s="3">
+        <v>700</v>
+      </c>
+      <c r="O22" s="3">
         <v>600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>3500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>5300</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1602,59 +1641,62 @@
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E23" s="3">
         <v>15700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>12900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-15800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>7200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>13700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>23700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>8400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-12900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4900</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1667,59 +1709,62 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>700</v>
+      </c>
+      <c r="E24" s="3">
         <v>2800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>11900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-12100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-3500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-5700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-500</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1732,8 +1777,11 @@
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1797,59 +1845,62 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E26" s="3">
         <v>12900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>11200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>19200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>8900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-14300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>5400</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1862,59 +1913,62 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E27" s="3">
         <v>12900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>11200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>19200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>8900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-14300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5400</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1927,8 +1981,11 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1992,8 +2049,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2057,8 +2117,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2122,8 +2185,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2187,59 +2253,62 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>600</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2252,59 +2321,62 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E33" s="3">
         <v>12900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>11200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>19200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>8900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-4700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-14300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>5400</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2317,8 +2389,11 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2382,59 +2457,62 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E35" s="3">
         <v>12900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>11200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>19200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>8900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-4700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-14300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>5400</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2447,64 +2525,67 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43830</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43738</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2517,8 +2598,11 @@
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2542,8 +2626,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2567,53 +2652,54 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>73800</v>
+      </c>
+      <c r="E41" s="3">
         <v>73300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>77600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>78000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>105200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>95600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>72200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>59800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>53300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>20900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>16400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>22600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>21000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>19500</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2632,8 +2718,11 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2697,53 +2786,56 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E43" s="3">
         <v>28200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>23800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>15300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>16200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>21200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>32900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>14500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>18200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>15300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>10100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>8900</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2762,8 +2854,11 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2827,53 +2922,56 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E45" s="3">
         <v>5900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5800</v>
-      </c>
-      <c r="J45" s="3">
-        <v>3700</v>
       </c>
       <c r="K45" s="3">
         <v>3700</v>
       </c>
       <c r="L45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="M45" s="3">
         <v>3200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4600</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2892,53 +2990,56 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>90200</v>
+      </c>
+      <c r="E46" s="3">
         <v>107400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>108300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>96600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>124900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>121700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>111000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>78000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>75200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>39400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>31000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>31400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>32500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>33000</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2957,37 +3058,40 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L47" s="3">
-        <v>7100</v>
+        <v>10100</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>7100</v>
@@ -2995,8 +3099,8 @@
       <c r="N47" s="3">
         <v>7100</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
+      <c r="O47" s="3">
+        <v>7100</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
@@ -3013,8 +3117,8 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
@@ -3022,53 +3126,56 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>218600</v>
+      </c>
+      <c r="E48" s="3">
         <v>210000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>199400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>188500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>180800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>174200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>176400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>178500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>181200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>179700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>184700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>182800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>187600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>190500</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3087,53 +3194,56 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E49" s="3">
         <v>15000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>15300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>15500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>15800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>15900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>13700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>13900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>14100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>15000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>13400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>13700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>14000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>14500</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3152,8 +3262,11 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3217,8 +3330,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3282,53 +3398,56 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E52" s="3">
         <v>13200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>13400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>23700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>10900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>12200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>13200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>16600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>16000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>18500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>15400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>18200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>19200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>13600</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3347,8 +3466,11 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3412,53 +3534,56 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>350200</v>
+      </c>
+      <c r="E54" s="3">
         <v>345600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>336300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>324300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>332300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>323900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>314300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>287000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>286500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>259700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>251600</v>
-      </c>
-      <c r="N54" s="3">
-        <v>253400</v>
       </c>
       <c r="O54" s="3">
         <v>253400</v>
       </c>
       <c r="P54" s="3">
+        <v>253400</v>
+      </c>
+      <c r="Q54" s="3">
         <v>251500</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3477,8 +3602,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3502,8 +3630,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3527,53 +3656,54 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E57" s="3">
         <v>6100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4400</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3592,8 +3722,11 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3604,10 +3737,10 @@
         <v>7900</v>
       </c>
       <c r="F58" s="3">
+        <v>7900</v>
+      </c>
+      <c r="G58" s="3">
         <v>8000</v>
-      </c>
-      <c r="G58" s="3">
-        <v>7900</v>
       </c>
       <c r="H58" s="3">
         <v>7900</v>
@@ -3616,29 +3749,29 @@
         <v>7900</v>
       </c>
       <c r="J58" s="3">
-        <v>7800</v>
+        <v>7900</v>
       </c>
       <c r="K58" s="3">
         <v>7800</v>
       </c>
       <c r="L58" s="3">
-        <v>9600</v>
+        <v>7800</v>
       </c>
       <c r="M58" s="3">
         <v>9600</v>
       </c>
       <c r="N58" s="3">
-        <v>9500</v>
+        <v>9600</v>
       </c>
       <c r="O58" s="3">
         <v>9500</v>
       </c>
       <c r="P58" s="3">
+        <v>9500</v>
+      </c>
+      <c r="Q58" s="3">
         <v>9400</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3657,53 +3790,56 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E59" s="3">
         <v>16200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>22000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>12700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>15900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>19100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>19900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>13200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>13000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>12600</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3722,53 +3858,56 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>29400</v>
+      </c>
+      <c r="E60" s="3">
         <v>30200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>35000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>23900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>28400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>30300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>32300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>26100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>24600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>29000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>29100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>26000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>28500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>26400</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3787,53 +3926,56 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>55600</v>
+      </c>
+      <c r="E61" s="3">
         <v>57600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>59600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>61500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>63500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>65500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>67500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>69400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>71400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>49000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>51400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>53900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>56300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>58700</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3852,53 +3994,56 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E62" s="3">
         <v>14600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>14000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>13300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>8000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>9000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>9600</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3917,8 +4062,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3982,8 +4130,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4047,8 +4198,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4112,53 +4266,56 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E66" s="3">
         <v>102400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>108500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>99300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>105200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>105100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>109400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>103600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>104200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>85700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>89000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>88600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>93700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>94700</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4177,8 +4334,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4202,8 +4362,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4267,8 +4428,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4332,8 +4496,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4397,8 +4564,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4462,47 +4632,50 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>45600</v>
+      </c>
+      <c r="E72" s="3">
         <v>40800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>27900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>26900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>30700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>24700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>13500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-5600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-4500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-10000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-18900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-14300</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4518,8 +4691,8 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U72" s="3">
-        <v>0</v>
+      <c r="U72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V72" s="3">
         <v>0</v>
@@ -4527,8 +4700,11 @@
       <c r="W72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4592,8 +4768,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4657,8 +4836,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4722,53 +4904,56 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>250200</v>
+      </c>
+      <c r="E76" s="3">
         <v>243200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>227800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>225100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>227100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>218800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>204900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>183400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>182300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>174100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>162600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>164700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>159600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>156900</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4787,8 +4972,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4852,64 +5040,67 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43830</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43738</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4922,59 +5113,62 @@
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E81" s="3">
         <v>12900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>11200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>19200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>8900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-4700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-14300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>5400</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4987,8 +5181,11 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5012,19 +5209,20 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="E83" s="3">
         <v>5300</v>
       </c>
       <c r="F83" s="3">
-        <v>5200</v>
+        <v>5300</v>
       </c>
       <c r="G83" s="3">
         <v>5200</v>
@@ -5033,16 +5231,16 @@
         <v>5200</v>
       </c>
       <c r="I83" s="3">
+        <v>5200</v>
+      </c>
+      <c r="J83" s="3">
         <v>5100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5800</v>
-      </c>
-      <c r="L83" s="3">
-        <v>5700</v>
       </c>
       <c r="M83" s="3">
         <v>5700</v>
@@ -5051,20 +5249,20 @@
         <v>5700</v>
       </c>
       <c r="O83" s="3">
+        <v>5700</v>
+      </c>
+      <c r="P83" s="3">
         <v>6000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>16100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>14800</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5077,8 +5275,11 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5142,8 +5343,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5207,8 +5411,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5272,8 +5479,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5337,8 +5547,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5402,59 +5615,62 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E89" s="3">
         <v>13500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>17900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-11800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>21300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>33000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>17200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>9600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>21600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>10100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>7800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>21900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>6200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>21700</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5467,8 +5683,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5492,59 +5711,60 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-15800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-16300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-13300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-11600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-33600</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5557,8 +5777,11 @@
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5622,8 +5845,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5687,59 +5913,62 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-15800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-16300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-9500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-7300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-13100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-12500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-32100</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5752,8 +5981,11 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5777,8 +6009,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5842,8 +6075,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5907,8 +6143,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5972,8 +6211,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6037,13 +6279,16 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2000</v>
+        <v>-3300</v>
       </c>
       <c r="E100" s="3">
         <v>-2000</v>
@@ -6052,44 +6297,44 @@
         <v>-2000</v>
       </c>
       <c r="G100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="H100" s="3">
         <v>-2200</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-2000</v>
       </c>
       <c r="I100" s="3">
         <v>-2000</v>
       </c>
       <c r="J100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="K100" s="3">
         <v>-2100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>18500</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-2500</v>
       </c>
       <c r="M100" s="3">
         <v>-2500</v>
       </c>
       <c r="N100" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="O100" s="3">
         <v>-4900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>13500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-41000</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6102,8 +6347,11 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6167,59 +6415,62 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-27100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>9600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>23500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>12400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>32000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-6300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>9900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>6800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-51400</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6230,6 +6481,9 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MNTK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MNTK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="92">
   <si>
     <t>MNTK</t>
   </si>
@@ -656,91 +656,92 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -753,62 +754,65 @@
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>38800</v>
+      </c>
+      <c r="E8" s="3">
         <v>46800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>55700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>53300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>19200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>49600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>55900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>67900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>32200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>45300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>39700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>31700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>31400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>24800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>75600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>22000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>83700</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
@@ -821,62 +825,65 @@
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E9" s="3">
         <v>25400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>25700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>25400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>18100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>24700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>26300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>30000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>20400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>22400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>19800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>19200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>16800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>16100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>45700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>12200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>46500</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
@@ -889,62 +896,65 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E10" s="3">
         <v>21400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>30000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>27900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>24900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>29600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>37900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>11800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>22900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>19900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>12500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>14600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>8700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>29900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>9800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>37200</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
@@ -957,8 +967,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -983,8 +996,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1051,8 +1065,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1119,62 +1136,65 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>600</v>
+      </c>
+      <c r="E14" s="3">
         <v>200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2300</v>
-      </c>
-      <c r="J14" s="3">
-        <v>100</v>
       </c>
       <c r="K14" s="3">
         <v>100</v>
       </c>
       <c r="L14" s="3">
+        <v>100</v>
+      </c>
+      <c r="M14" s="3">
         <v>700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>200</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>600</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1600</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1187,8 +1207,11 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1196,13 +1219,13 @@
         <v>5400</v>
       </c>
       <c r="E15" s="3">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="F15" s="3">
         <v>5300</v>
       </c>
       <c r="G15" s="3">
-        <v>5200</v>
+        <v>5300</v>
       </c>
       <c r="H15" s="3">
         <v>5200</v>
@@ -1211,16 +1234,16 @@
         <v>5200</v>
       </c>
       <c r="J15" s="3">
+        <v>5200</v>
+      </c>
+      <c r="K15" s="3">
         <v>5100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>5200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>5800</v>
-      </c>
-      <c r="M15" s="3">
-        <v>5700</v>
       </c>
       <c r="N15" s="3">
         <v>5700</v>
@@ -1229,20 +1252,20 @@
         <v>5700</v>
       </c>
       <c r="P15" s="3">
+        <v>5700</v>
+      </c>
+      <c r="Q15" s="3">
         <v>6000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>16100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>5000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>14800</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1255,8 +1278,11 @@
       <c r="X15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1278,62 +1304,63 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>36400</v>
+      </c>
+      <c r="E17" s="3">
         <v>39300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>38900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>39700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>33300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>41000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>42200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>43900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>33800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>36100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>33000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>32200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>43700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>26900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>69900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>21100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>73600</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1346,62 +1373,65 @@
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E18" s="3">
         <v>7500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>16800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>13600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-14100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>8600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>13700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>24000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>9200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>6700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-12300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>5700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>10100</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1414,8 +1444,11 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1440,62 +1473,63 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-600</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1508,62 +1542,65 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E21" s="3">
         <v>13000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>22400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>18900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-9000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>13900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>18900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>29100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>15000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>11800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-6500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>21500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>25000</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1576,62 +1613,65 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E22" s="3">
         <v>2100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1500</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
       <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
         <v>300</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
         <v>900</v>
-      </c>
-      <c r="M22" s="3">
-        <v>700</v>
       </c>
       <c r="N22" s="3">
         <v>700</v>
       </c>
       <c r="O22" s="3">
+        <v>700</v>
+      </c>
+      <c r="P22" s="3">
         <v>600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>3500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>5300</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1644,62 +1684,65 @@
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E23" s="3">
         <v>5500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>15700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>12900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-15800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>7200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>13700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>23700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-12900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4900</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1712,62 +1755,65 @@
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>400</v>
+      </c>
+      <c r="E24" s="3">
         <v>700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>11900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-12100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-3500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-500</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1780,8 +1826,11 @@
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1848,62 +1897,65 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E26" s="3">
         <v>4800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>12900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>11200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>19200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>8900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-14300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>5400</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1916,62 +1968,65 @@
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E27" s="3">
         <v>4800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>12900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>11200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>19200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>8900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-14300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5400</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1984,8 +2039,11 @@
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2052,8 +2110,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2120,8 +2181,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2188,8 +2252,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2256,62 +2323,65 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>600</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2324,62 +2394,65 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E33" s="3">
         <v>4800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>12900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>11200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>19200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>8900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-14300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5400</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2392,8 +2465,11 @@
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2460,62 +2536,65 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E35" s="3">
         <v>4800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>12900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>11200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>19200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>8900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-14300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5400</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2528,67 +2607,70 @@
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2601,8 +2683,11 @@
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2627,8 +2712,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2653,56 +2739,57 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>63300</v>
+      </c>
+      <c r="E41" s="3">
         <v>73800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>73300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>77600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>78000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>105200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>95600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>72200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>59800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>53300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>20900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>16400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>22600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>21000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>19500</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2721,8 +2808,11 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2789,56 +2879,59 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E43" s="3">
         <v>12700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>28200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>23800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>15300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>16200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>21200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>32900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>14500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>18200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>15300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>10100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>8900</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2857,8 +2950,11 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2925,56 +3021,59 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E45" s="3">
         <v>3700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5800</v>
-      </c>
-      <c r="K45" s="3">
-        <v>3700</v>
       </c>
       <c r="L45" s="3">
         <v>3700</v>
       </c>
       <c r="M45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="N45" s="3">
         <v>3200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4600</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2993,56 +3092,59 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>76600</v>
+      </c>
+      <c r="E46" s="3">
         <v>90200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>107400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>108300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>96600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>124900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>121700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>111000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>78000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>75200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>39400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>31000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>31400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>32500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>33000</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3061,16 +3163,19 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
         <v>10100</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>3</v>
+      <c r="E47" s="3">
+        <v>10100</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>3</v>
@@ -3087,14 +3192,14 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M47" s="3">
-        <v>7100</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>7100</v>
@@ -3102,8 +3207,8 @@
       <c r="O47" s="3">
         <v>7100</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
+      <c r="P47" s="3">
+        <v>7100</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
@@ -3120,8 +3225,8 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
+      <c r="V47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
@@ -3129,56 +3234,59 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>235700</v>
+      </c>
+      <c r="E48" s="3">
         <v>218600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>210000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>199400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>188500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>180800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>174200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>176400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>178500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>181200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>179700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>184700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>182800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>187600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>190500</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3197,56 +3305,59 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E49" s="3">
         <v>18400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>15000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>15300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>15500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>15800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>15900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>13700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>13900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>15000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>13400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>13700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>14000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>14500</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3265,8 +3376,11 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3333,8 +3447,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3401,56 +3518,59 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E52" s="3">
         <v>12900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>13200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>13400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>23700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>10900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>12200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>13200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>16600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>16000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>18500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>15400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>18200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>19200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>13600</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3469,8 +3589,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3537,56 +3660,59 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>354700</v>
+      </c>
+      <c r="E54" s="3">
         <v>350200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>345600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>336300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>324300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>332300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>323900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>314300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>287000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>286500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>259700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>251600</v>
-      </c>
-      <c r="O54" s="3">
-        <v>253400</v>
       </c>
       <c r="P54" s="3">
         <v>253400</v>
       </c>
       <c r="Q54" s="3">
+        <v>253400</v>
+      </c>
+      <c r="R54" s="3">
         <v>251500</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3605,8 +3731,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3631,8 +3760,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3657,56 +3787,57 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E57" s="3">
         <v>7900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4400</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3725,13 +3856,16 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>7900</v>
+        <v>8900</v>
       </c>
       <c r="E58" s="3">
         <v>7900</v>
@@ -3740,10 +3874,10 @@
         <v>7900</v>
       </c>
       <c r="G58" s="3">
+        <v>7900</v>
+      </c>
+      <c r="H58" s="3">
         <v>8000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>7900</v>
       </c>
       <c r="I58" s="3">
         <v>7900</v>
@@ -3752,29 +3886,29 @@
         <v>7900</v>
       </c>
       <c r="K58" s="3">
-        <v>7800</v>
+        <v>7900</v>
       </c>
       <c r="L58" s="3">
         <v>7800</v>
       </c>
       <c r="M58" s="3">
-        <v>9600</v>
+        <v>7800</v>
       </c>
       <c r="N58" s="3">
         <v>9600</v>
       </c>
       <c r="O58" s="3">
-        <v>9500</v>
+        <v>9600</v>
       </c>
       <c r="P58" s="3">
         <v>9500</v>
       </c>
       <c r="Q58" s="3">
+        <v>9500</v>
+      </c>
+      <c r="R58" s="3">
         <v>9400</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3793,56 +3927,59 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E59" s="3">
         <v>13500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>16200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>22000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>15900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>19100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>19900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>13000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>12600</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3861,56 +3998,59 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E60" s="3">
         <v>29400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>30200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>35000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>23900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>28400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>30300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>32300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>26100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>24600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>29000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>29100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>26000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>28500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>26400</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3929,56 +4069,59 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>52700</v>
+      </c>
+      <c r="E61" s="3">
         <v>55600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>57600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>59600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>61500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>63500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>65500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>67500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>69400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>71400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>49000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>51400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>53900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>56300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>58700</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3997,56 +4140,59 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E62" s="3">
         <v>15000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>14600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>14000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>13900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>13300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>8700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>9000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>9600</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4065,8 +4211,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4133,8 +4282,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4201,8 +4353,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4269,56 +4424,59 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>100400</v>
+      </c>
+      <c r="E66" s="3">
         <v>100000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>102400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>108500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>99300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>105200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>105100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>109400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>103600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>104200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>85700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>89000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>88600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>93700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>94700</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4337,8 +4495,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4363,8 +4524,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4431,8 +4593,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4499,8 +4664,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4567,8 +4735,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4635,50 +4806,53 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>47500</v>
+      </c>
+      <c r="E72" s="3">
         <v>45600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>40800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>27900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>26900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>30700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>24700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>13500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-5600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-4500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-10000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-18900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-14300</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4694,8 +4868,8 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V72" s="3">
-        <v>0</v>
+      <c r="V72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W72" s="3">
         <v>0</v>
@@ -4703,8 +4877,11 @@
       <c r="X72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4771,8 +4948,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4839,8 +5019,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4907,56 +5090,59 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>254300</v>
+      </c>
+      <c r="E76" s="3">
         <v>250200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>243200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>227800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>225100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>227100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>218800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>204900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>183400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>182300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>174100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>162600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>164700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>159600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>156900</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4975,8 +5161,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5043,67 +5232,70 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5116,62 +5308,65 @@
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E81" s="3">
         <v>4800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>12900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>11200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>19200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>8900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-14300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5400</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5184,8 +5379,11 @@
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5210,8 +5408,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5219,13 +5418,13 @@
         <v>5400</v>
       </c>
       <c r="E83" s="3">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="F83" s="3">
         <v>5300</v>
       </c>
       <c r="G83" s="3">
-        <v>5200</v>
+        <v>5300</v>
       </c>
       <c r="H83" s="3">
         <v>5200</v>
@@ -5234,16 +5433,16 @@
         <v>5200</v>
       </c>
       <c r="J83" s="3">
+        <v>5200</v>
+      </c>
+      <c r="K83" s="3">
         <v>5100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5800</v>
-      </c>
-      <c r="M83" s="3">
-        <v>5700</v>
       </c>
       <c r="N83" s="3">
         <v>5700</v>
@@ -5252,20 +5451,20 @@
         <v>5700</v>
       </c>
       <c r="P83" s="3">
+        <v>5700</v>
+      </c>
+      <c r="Q83" s="3">
         <v>6000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>16100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>5000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>14800</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5278,8 +5477,11 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5346,8 +5548,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5414,8 +5619,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5482,8 +5690,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5550,8 +5761,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5618,62 +5832,65 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E89" s="3">
         <v>21500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>13500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>17900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-11800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>21300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>33000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>17200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>9600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>21600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>10100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>7800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>6700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>21900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>6200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>21700</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5686,8 +5903,11 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5712,62 +5932,63 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-17700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-15800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-16300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-13300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-7600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-14200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-11600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-33600</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5780,8 +6001,11 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5848,8 +6072,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5916,62 +6143,65 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-17700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-15800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-16300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-13300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-9500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-7300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-13100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-12500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-32100</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5984,8 +6214,11 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6010,8 +6243,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6078,8 +6312,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6146,8 +6383,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6214,8 +6454,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6282,16 +6525,19 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3300</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-2000</v>
       </c>
       <c r="F100" s="3">
         <v>-2000</v>
@@ -6300,44 +6546,44 @@
         <v>-2000</v>
       </c>
       <c r="H100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="I100" s="3">
         <v>-2200</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-2000</v>
       </c>
       <c r="J100" s="3">
         <v>-2000</v>
       </c>
       <c r="K100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="L100" s="3">
         <v>-2100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>18500</v>
-      </c>
-      <c r="M100" s="3">
-        <v>-2500</v>
       </c>
       <c r="N100" s="3">
         <v>-2500</v>
       </c>
       <c r="O100" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="P100" s="3">
         <v>-4900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>13500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-41000</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6350,8 +6596,11 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6418,62 +6667,65 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E102" s="3">
         <v>500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-27100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>9600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>23500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>12400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>32000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>4700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-6300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>9900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>6800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-51400</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6484,6 +6736,9 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MNTK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MNTK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="92">
   <si>
     <t>MNTK</t>
   </si>
@@ -656,95 +656,96 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
@@ -757,65 +758,68 @@
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>43300</v>
+      </c>
+      <c r="E8" s="3">
         <v>38800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>46800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>55700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>53300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>19200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>49600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>55900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>67900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>32200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>45300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>39700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>31700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>31400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>24800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>75600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>22000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>83700</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
@@ -828,65 +832,68 @@
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>27700</v>
+      </c>
+      <c r="E9" s="3">
         <v>21000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>25400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>25700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>25400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>18100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>24700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>26300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>30000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>20400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>22400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>19800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>19200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>16800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>16100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>45700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>12200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>46500</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
@@ -899,65 +906,68 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E10" s="3">
         <v>17800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>21400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>30000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>27900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>24900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>29600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>37900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>11800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>22900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>19900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>12500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>14600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>8700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>29900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>9800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>37200</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
@@ -970,8 +980,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -997,8 +1010,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1068,8 +1082,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1139,65 +1156,68 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>200</v>
+      </c>
+      <c r="E14" s="3">
         <v>600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2300</v>
-      </c>
-      <c r="K14" s="3">
-        <v>100</v>
       </c>
       <c r="L14" s="3">
         <v>100</v>
       </c>
       <c r="M14" s="3">
+        <v>100</v>
+      </c>
+      <c r="N14" s="3">
         <v>700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>200</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>600</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1600</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1210,25 +1230,28 @@
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>5400</v>
+        <v>5800</v>
       </c>
       <c r="E15" s="3">
         <v>5400</v>
       </c>
       <c r="F15" s="3">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="G15" s="3">
         <v>5300</v>
       </c>
       <c r="H15" s="3">
-        <v>5200</v>
+        <v>5300</v>
       </c>
       <c r="I15" s="3">
         <v>5200</v>
@@ -1237,16 +1260,16 @@
         <v>5200</v>
       </c>
       <c r="K15" s="3">
+        <v>5200</v>
+      </c>
+      <c r="L15" s="3">
         <v>5100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>5200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>5800</v>
-      </c>
-      <c r="N15" s="3">
-        <v>5700</v>
       </c>
       <c r="O15" s="3">
         <v>5700</v>
@@ -1255,20 +1278,20 @@
         <v>5700</v>
       </c>
       <c r="Q15" s="3">
+        <v>5700</v>
+      </c>
+      <c r="R15" s="3">
         <v>6000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>16100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>5000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>14800</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1281,8 +1304,11 @@
       <c r="Y15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1305,65 +1331,66 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>42500</v>
+      </c>
+      <c r="E17" s="3">
         <v>36400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>39300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>38900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>39700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>33300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>41000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>42200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>43900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>33800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>36100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>33000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>32200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>43700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>26900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>69900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>21100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>73600</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1376,65 +1403,68 @@
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>800</v>
+      </c>
+      <c r="E18" s="3">
         <v>2400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>7500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>16800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>13600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-14100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>8600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>13700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>24000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>9200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>6700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-12300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>5700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>10100</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1447,8 +1477,11 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1474,65 +1507,66 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-600</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1545,65 +1579,68 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E21" s="3">
         <v>8900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>13000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>22400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>18900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-9000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>13900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>18900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>29100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>15000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>11800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>21500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>25000</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1616,65 +1653,68 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E22" s="3">
         <v>1200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1500</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
       <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
         <v>300</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
         <v>900</v>
-      </c>
-      <c r="N22" s="3">
-        <v>700</v>
       </c>
       <c r="O22" s="3">
         <v>700</v>
       </c>
       <c r="P22" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q22" s="3">
         <v>600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>3500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>5300</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1687,65 +1727,68 @@
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E23" s="3">
         <v>2300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>15700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>12900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-15800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>13700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>23700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-12900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4900</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1758,65 +1801,68 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>300</v>
+      </c>
+      <c r="E24" s="3">
         <v>400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>11900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-12100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-3500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-5700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-500</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1829,8 +1875,11 @@
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1900,65 +1949,68 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E26" s="3">
         <v>1900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>12900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>6000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>11200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>19200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>8900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>5400</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1971,65 +2023,68 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E27" s="3">
         <v>1900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>12900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>6000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>11200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>19200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>8900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>5400</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2042,8 +2097,11 @@
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2113,8 +2171,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2184,8 +2245,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2255,8 +2319,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2326,65 +2393,68 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>600</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2397,65 +2467,68 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E33" s="3">
         <v>1900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>12900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>6000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>11200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>19200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>8900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5400</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2468,8 +2541,11 @@
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2539,65 +2615,68 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E35" s="3">
         <v>1900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>12900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>6000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>11200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>19200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>8900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5400</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2610,70 +2689,73 @@
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2686,8 +2768,11 @@
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2713,8 +2798,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2740,59 +2826,60 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>42300</v>
+      </c>
+      <c r="E41" s="3">
         <v>63300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>73800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>73300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>77600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>78000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>105200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>95600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>72200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>59800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>53300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>20900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>16400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>22600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>21000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>19500</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2811,8 +2898,11 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2882,59 +2972,62 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E43" s="3">
         <v>9700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>12700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>28200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>23800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>15300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>16200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>21200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>32900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>14500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>18200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>15300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>10100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>8900</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2953,8 +3046,11 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3024,59 +3120,62 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E45" s="3">
         <v>3600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5800</v>
-      </c>
-      <c r="L45" s="3">
-        <v>3700</v>
       </c>
       <c r="M45" s="3">
         <v>3700</v>
       </c>
       <c r="N45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="O45" s="3">
         <v>3200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4600</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3095,59 +3194,62 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>71100</v>
+      </c>
+      <c r="E46" s="3">
         <v>76600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>90200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>107400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>108300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>96600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>124900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>121700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>111000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>78000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>75200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>39400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>31000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>31400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>32500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>33000</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3166,19 +3268,22 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>10100</v>
+        <v>10200</v>
       </c>
       <c r="E47" s="3">
         <v>10100</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
+      <c r="F47" s="3">
+        <v>10100</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
@@ -3195,14 +3300,14 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N47" s="3">
-        <v>7100</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O47" s="3">
         <v>7100</v>
@@ -3210,8 +3315,8 @@
       <c r="P47" s="3">
         <v>7100</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
+      <c r="Q47" s="3">
+        <v>7100</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
@@ -3228,8 +3333,8 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W47" s="3">
-        <v>0</v>
+      <c r="W47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X47" s="3">
         <v>0</v>
@@ -3237,59 +3342,62 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>248700</v>
+      </c>
+      <c r="E48" s="3">
         <v>235700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>218600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>210000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>199400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>188500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>180800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>174200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>176400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>178500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>181200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>179700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>184700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>182800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>187600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>190500</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3308,59 +3416,62 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E49" s="3">
         <v>18200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>18400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>15000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>15300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>15500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>15800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>15900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>13700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>13900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>14100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>15000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>13400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>13700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>14000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>14500</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3379,8 +3490,11 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3450,8 +3564,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3521,8 +3638,11 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3530,50 +3650,50 @@
         <v>14100</v>
       </c>
       <c r="E52" s="3">
+        <v>14100</v>
+      </c>
+      <c r="F52" s="3">
         <v>12900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>13200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>13400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>23700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>10900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>12200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>13200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>16600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>16000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>18500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>15400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>18200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>19200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>13600</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3592,8 +3712,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3663,59 +3786,62 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>362000</v>
+      </c>
+      <c r="E54" s="3">
         <v>354700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>350200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>345600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>336300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>324300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>332300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>323900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>314300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>287000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>286500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>259700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>251600</v>
-      </c>
-      <c r="P54" s="3">
-        <v>253400</v>
       </c>
       <c r="Q54" s="3">
         <v>253400</v>
       </c>
       <c r="R54" s="3">
+        <v>253400</v>
+      </c>
+      <c r="S54" s="3">
         <v>251500</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3734,8 +3860,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3761,8 +3890,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3788,59 +3918,60 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E57" s="3">
         <v>12300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4400</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3859,16 +3990,19 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E58" s="3">
         <v>8900</v>
-      </c>
-      <c r="E58" s="3">
-        <v>7900</v>
       </c>
       <c r="F58" s="3">
         <v>7900</v>
@@ -3877,10 +4011,10 @@
         <v>7900</v>
       </c>
       <c r="H58" s="3">
+        <v>7900</v>
+      </c>
+      <c r="I58" s="3">
         <v>8000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>7900</v>
       </c>
       <c r="J58" s="3">
         <v>7900</v>
@@ -3889,29 +4023,29 @@
         <v>7900</v>
       </c>
       <c r="L58" s="3">
-        <v>7800</v>
+        <v>7900</v>
       </c>
       <c r="M58" s="3">
         <v>7800</v>
       </c>
       <c r="N58" s="3">
-        <v>9600</v>
+        <v>7800</v>
       </c>
       <c r="O58" s="3">
         <v>9600</v>
       </c>
       <c r="P58" s="3">
-        <v>9500</v>
+        <v>9600</v>
       </c>
       <c r="Q58" s="3">
         <v>9500</v>
       </c>
       <c r="R58" s="3">
+        <v>9500</v>
+      </c>
+      <c r="S58" s="3">
         <v>9400</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3930,59 +4064,62 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E59" s="3">
         <v>12600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>13500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>16200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>22000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>15900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>19100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>19900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>13000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>12600</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4001,59 +4138,62 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>42900</v>
+      </c>
+      <c r="E60" s="3">
         <v>33800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>29400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>30200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>35000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>23900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>28400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>30300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>32300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>26100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>24600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>29000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>29100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>26000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>28500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>26400</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4072,59 +4212,62 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>49800</v>
+      </c>
+      <c r="E61" s="3">
         <v>52700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>55600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>57600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>59600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>61500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>63500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>65500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>67500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>69400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>71400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>49000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>51400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>53900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>56300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>58700</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4143,59 +4286,62 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E62" s="3">
         <v>13900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>15000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>14600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>14000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>13900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>13300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>8500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>8700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>9000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>9600</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4214,8 +4360,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4285,8 +4434,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4356,8 +4508,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4427,59 +4582,62 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>106700</v>
+      </c>
+      <c r="E66" s="3">
         <v>100400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>100000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>102400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>108500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>99300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>105200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>105100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>109400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>103600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>104200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>85700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>89000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>88600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>93700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>94700</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4498,8 +4656,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4525,8 +4686,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4596,8 +4758,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4667,8 +4832,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4738,8 +4906,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4809,53 +4980,56 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>46800</v>
+      </c>
+      <c r="E72" s="3">
         <v>47500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>45600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>40800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>27900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>26900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>30700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>24700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>13500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-5600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-4500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-10000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-18900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4871,8 +5045,8 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W72" s="3">
-        <v>0</v>
+      <c r="W72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X72" s="3">
         <v>0</v>
@@ -4880,8 +5054,11 @@
       <c r="Y72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4951,8 +5128,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5022,8 +5202,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5093,59 +5276,62 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>255300</v>
+      </c>
+      <c r="E76" s="3">
         <v>254300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>250200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>243200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>227800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>225100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>227100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>218800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>204900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>183400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>182300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>174100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>162600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>164700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>159600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>156900</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5164,8 +5350,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5235,70 +5424,73 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5311,65 +5503,68 @@
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E81" s="3">
         <v>1900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>12900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>6000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>11200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>19200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>8900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5400</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5382,8 +5577,11 @@
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5409,25 +5607,26 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>5400</v>
+        <v>5800</v>
       </c>
       <c r="E83" s="3">
         <v>5400</v>
       </c>
       <c r="F83" s="3">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="G83" s="3">
         <v>5300</v>
       </c>
       <c r="H83" s="3">
-        <v>5200</v>
+        <v>5300</v>
       </c>
       <c r="I83" s="3">
         <v>5200</v>
@@ -5436,16 +5635,16 @@
         <v>5200</v>
       </c>
       <c r="K83" s="3">
+        <v>5200</v>
+      </c>
+      <c r="L83" s="3">
         <v>5100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5800</v>
-      </c>
-      <c r="N83" s="3">
-        <v>5700</v>
       </c>
       <c r="O83" s="3">
         <v>5700</v>
@@ -5454,20 +5653,20 @@
         <v>5700</v>
       </c>
       <c r="Q83" s="3">
+        <v>5700</v>
+      </c>
+      <c r="R83" s="3">
         <v>6000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>16100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>5000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>14800</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5480,8 +5679,11 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5551,8 +5753,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5622,8 +5827,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5693,8 +5901,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5764,8 +5975,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5835,65 +6049,68 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>200</v>
+      </c>
+      <c r="E89" s="3">
         <v>14300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>21500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>13500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>17900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-11800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>21300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>33000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>17200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>9600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>21600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>10100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>7800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>6700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>21900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>6200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>21700</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5906,8 +6123,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5933,65 +6153,66 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-22000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-17700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-15800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-16300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-13300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-9500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-14200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-11600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-33600</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6004,8 +6225,11 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6075,8 +6299,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6146,65 +6373,68 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-22800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-17700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-15800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-16300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-13300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-9500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-8100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-7300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-13100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-12500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-32100</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6217,8 +6447,11 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6244,8 +6477,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6315,8 +6549,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6386,8 +6623,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6457,8 +6697,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6528,19 +6771,22 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3300</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-2000</v>
       </c>
       <c r="G100" s="3">
         <v>-2000</v>
@@ -6549,44 +6795,44 @@
         <v>-2000</v>
       </c>
       <c r="I100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J100" s="3">
         <v>-2200</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-2000</v>
       </c>
       <c r="K100" s="3">
         <v>-2000</v>
       </c>
       <c r="L100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="M100" s="3">
         <v>-2100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>18500</v>
-      </c>
-      <c r="N100" s="3">
-        <v>-2500</v>
       </c>
       <c r="O100" s="3">
         <v>-2500</v>
       </c>
       <c r="P100" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>13500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-41000</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6599,8 +6845,11 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6670,65 +6919,68 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-10500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-27100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>9600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>23500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>12400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>32000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>4700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-6300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>9900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>6800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-51400</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6739,6 +6991,9 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MNTK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MNTK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="92">
   <si>
     <t>MNTK</t>
   </si>
@@ -656,99 +656,100 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
@@ -761,68 +762,71 @@
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>65900</v>
+      </c>
+      <c r="E8" s="3">
         <v>43300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>38800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>46800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>55700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>53300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>19200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>49600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>55900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>67900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>32200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>45300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>39700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>31700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>31400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>24800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>75600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>22000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>83700</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
@@ -835,68 +839,71 @@
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E9" s="3">
         <v>27700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>21000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>25400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>25700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>25400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>18100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>24700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>26300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>30000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>20400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>22400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>19800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>19200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>16800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>16100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>45700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>12200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>46500</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
@@ -909,68 +916,71 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E10" s="3">
         <v>15600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>17800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>21400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>30000</v>
       </c>
-      <c r="H10" s="3">
-        <v>27900</v>
-      </c>
       <c r="I10" s="3">
-        <v>1100</v>
+        <v>27800</v>
       </c>
       <c r="J10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K10" s="3">
         <v>24900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>29600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>37900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>11800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>22900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>19900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>12500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>14600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>8700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>29900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>9800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>37200</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
@@ -983,8 +993,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1011,8 +1024,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1085,8 +1099,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1159,68 +1176,71 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E14" s="3">
         <v>200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2300</v>
-      </c>
-      <c r="L14" s="3">
-        <v>100</v>
       </c>
       <c r="M14" s="3">
         <v>100</v>
       </c>
       <c r="N14" s="3">
+        <v>100</v>
+      </c>
+      <c r="O14" s="3">
         <v>700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>200</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>600</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1600</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1233,28 +1253,31 @@
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E15" s="3">
         <v>5800</v>
-      </c>
-      <c r="E15" s="3">
-        <v>5400</v>
       </c>
       <c r="F15" s="3">
         <v>5400</v>
       </c>
       <c r="G15" s="3">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="H15" s="3">
         <v>5300</v>
       </c>
       <c r="I15" s="3">
-        <v>5200</v>
+        <v>5300</v>
       </c>
       <c r="J15" s="3">
         <v>5200</v>
@@ -1263,16 +1286,16 @@
         <v>5200</v>
       </c>
       <c r="L15" s="3">
+        <v>5200</v>
+      </c>
+      <c r="M15" s="3">
         <v>5100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>5200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>5800</v>
-      </c>
-      <c r="O15" s="3">
-        <v>5700</v>
       </c>
       <c r="P15" s="3">
         <v>5700</v>
@@ -1281,20 +1304,20 @@
         <v>5700</v>
       </c>
       <c r="R15" s="3">
+        <v>5700</v>
+      </c>
+      <c r="S15" s="3">
         <v>6000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>16100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>5000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>14800</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1307,8 +1330,11 @@
       <c r="Z15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1332,68 +1358,69 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>42500</v>
+        <v>39800</v>
       </c>
       <c r="E17" s="3">
-        <v>36400</v>
+        <v>42300</v>
       </c>
       <c r="F17" s="3">
-        <v>39300</v>
+        <v>35800</v>
       </c>
       <c r="G17" s="3">
+        <v>39100</v>
+      </c>
+      <c r="H17" s="3">
         <v>38900</v>
       </c>
-      <c r="H17" s="3">
-        <v>39700</v>
-      </c>
       <c r="I17" s="3">
-        <v>33300</v>
+        <v>39400</v>
       </c>
       <c r="J17" s="3">
+        <v>32800</v>
+      </c>
+      <c r="K17" s="3">
         <v>41000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>42200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>43900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>33800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>36100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>33000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>32200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>43700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>26900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>69900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>21100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>73600</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1406,68 +1433,71 @@
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>800</v>
+        <v>26200</v>
       </c>
       <c r="E18" s="3">
-        <v>2400</v>
+        <v>1000</v>
       </c>
       <c r="F18" s="3">
-        <v>7500</v>
+        <v>3000</v>
       </c>
       <c r="G18" s="3">
+        <v>7700</v>
+      </c>
+      <c r="H18" s="3">
         <v>16800</v>
       </c>
-      <c r="H18" s="3">
-        <v>13600</v>
-      </c>
       <c r="I18" s="3">
-        <v>-14100</v>
+        <v>13800</v>
       </c>
       <c r="J18" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="K18" s="3">
         <v>8600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>13700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>24000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>9200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-12300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>5700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>10100</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1480,8 +1510,11 @@
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1508,25 +1541,26 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
-        <v>1000</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="3">
-        <v>100</v>
+        <v>-1100</v>
       </c>
       <c r="G20" s="3">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="I20" s="3">
         <v>-100</v>
@@ -1535,41 +1569,41 @@
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>300</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-600</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1582,68 +1616,71 @@
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>6700</v>
+        <v>32300</v>
       </c>
       <c r="E21" s="3">
-        <v>8900</v>
+        <v>6900</v>
       </c>
       <c r="F21" s="3">
-        <v>13000</v>
+        <v>9500</v>
       </c>
       <c r="G21" s="3">
+        <v>13200</v>
+      </c>
+      <c r="H21" s="3">
         <v>22400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>19200</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="K21" s="3">
+        <v>13900</v>
+      </c>
+      <c r="L21" s="3">
         <v>18900</v>
       </c>
-      <c r="I21" s="3">
-        <v>-9000</v>
-      </c>
-      <c r="J21" s="3">
-        <v>13900</v>
-      </c>
-      <c r="K21" s="3">
-        <v>18900</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>29100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>15000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>11800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-6500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>21500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>25000</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1656,68 +1693,71 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E22" s="3">
         <v>1300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1500</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
         <v>300</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
         <v>900</v>
-      </c>
-      <c r="O22" s="3">
-        <v>700</v>
       </c>
       <c r="P22" s="3">
         <v>700</v>
       </c>
       <c r="Q22" s="3">
+        <v>700</v>
+      </c>
+      <c r="R22" s="3">
         <v>600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>3500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>5300</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1730,68 +1770,71 @@
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>15700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>12900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-15800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>13700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>23700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>8400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-12900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4900</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1804,68 +1847,71 @@
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>11900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-12100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-3500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-5700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-500</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1878,8 +1924,11 @@
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1952,68 +2001,71 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>12900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>11200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>19200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>8900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-14300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>5400</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2026,68 +2078,71 @@
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>12900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>6000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>11200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>19200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>8900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-14300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>5400</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2100,8 +2155,11 @@
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2174,8 +2232,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2248,8 +2309,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2322,8 +2386,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2396,25 +2463,28 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
-        <v>-1000</v>
+        <v>100</v>
       </c>
       <c r="F32" s="3">
-        <v>-100</v>
+        <v>1100</v>
       </c>
       <c r="G32" s="3">
-        <v>-200</v>
+        <v>100</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I32" s="3">
         <v>100</v>
@@ -2423,41 +2493,41 @@
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-300</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>600</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2470,68 +2540,71 @@
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>12900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>6000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>11200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>19200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>8900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-14300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>5400</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2544,8 +2617,11 @@
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2618,68 +2694,71 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>12900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>6000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>11200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>19200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>8900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-14300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>5400</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2692,73 +2771,76 @@
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2771,8 +2853,11 @@
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2799,8 +2884,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2827,62 +2913,63 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>55000</v>
+      </c>
+      <c r="E41" s="3">
         <v>42300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>63300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>73800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>73300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>77600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>78000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>105200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>95600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>72200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>59800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>53300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>20900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>16400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>22600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>21000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>19500</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2901,31 +2988,34 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2975,62 +3065,65 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>22400</v>
+        <v>19200</v>
       </c>
       <c r="E43" s="3">
-        <v>9700</v>
+        <v>22500</v>
       </c>
       <c r="F43" s="3">
-        <v>12700</v>
+        <v>9800</v>
       </c>
       <c r="G43" s="3">
+        <v>12800</v>
+      </c>
+      <c r="H43" s="3">
         <v>28200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>23800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>15300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>16200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>21200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>32900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>14500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>18200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>15300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>10100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>8900</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3049,31 +3142,34 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3123,62 +3219,65 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>6500</v>
-      </c>
-      <c r="E45" s="3">
-        <v>3600</v>
-      </c>
-      <c r="F45" s="3">
-        <v>3700</v>
-      </c>
-      <c r="G45" s="3">
-        <v>5900</v>
-      </c>
-      <c r="H45" s="3">
-        <v>6900</v>
-      </c>
-      <c r="I45" s="3">
-        <v>3300</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>3500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5800</v>
-      </c>
-      <c r="M45" s="3">
-        <v>3700</v>
       </c>
       <c r="N45" s="3">
         <v>3700</v>
       </c>
       <c r="O45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="P45" s="3">
         <v>3200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4600</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3197,62 +3296,65 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>79300</v>
+      </c>
+      <c r="E46" s="3">
         <v>71100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>76600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>90200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>107400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>108300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>96600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>124900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>121700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>111000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>78000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>75200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>39400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>31000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>31400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>32500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>33000</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3271,31 +3373,34 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>10200</v>
+        <v>200</v>
       </c>
       <c r="E47" s="3">
-        <v>10100</v>
+        <v>500</v>
       </c>
       <c r="F47" s="3">
-        <v>10100</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
+        <v>600</v>
+      </c>
+      <c r="G47" s="3">
+        <v>500</v>
+      </c>
+      <c r="H47" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I47" s="3">
+        <v>900</v>
+      </c>
+      <c r="J47" s="3">
+        <v>600</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -3303,14 +3408,14 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O47" s="3">
-        <v>7100</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>7100</v>
@@ -3318,8 +3423,8 @@
       <c r="Q47" s="3">
         <v>7100</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
+      <c r="R47" s="3">
+        <v>7100</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
@@ -3336,8 +3441,8 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X47" s="3">
-        <v>0</v>
+      <c r="X47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y47" s="3">
         <v>0</v>
@@ -3345,62 +3450,65 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>254000</v>
+      </c>
+      <c r="E48" s="3">
         <v>248700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>235700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>218600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>210000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>199400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>188500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>180800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>174200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>176400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>178500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>181200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>179700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>184700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>182800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>187600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>190500</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3419,62 +3527,65 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E49" s="3">
         <v>17900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>18200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>18400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>15000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>15300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>15500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>15800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>15900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>13700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>13900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>14100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>15000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>13400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>13700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>14000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>14500</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3493,8 +3604,11 @@
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3567,8 +3681,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3641,62 +3758,65 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>14100</v>
+        <v>12000</v>
       </c>
       <c r="E52" s="3">
-        <v>14100</v>
+        <v>11600</v>
       </c>
       <c r="F52" s="3">
-        <v>12900</v>
+        <v>11700</v>
       </c>
       <c r="G52" s="3">
+        <v>20500</v>
+      </c>
+      <c r="H52" s="3">
+        <v>10100</v>
+      </c>
+      <c r="I52" s="3">
+        <v>8600</v>
+      </c>
+      <c r="J52" s="3">
+        <v>6100</v>
+      </c>
+      <c r="K52" s="3">
+        <v>10900</v>
+      </c>
+      <c r="L52" s="3">
+        <v>12200</v>
+      </c>
+      <c r="M52" s="3">
         <v>13200</v>
       </c>
-      <c r="H52" s="3">
-        <v>13400</v>
-      </c>
-      <c r="I52" s="3">
-        <v>23700</v>
-      </c>
-      <c r="J52" s="3">
-        <v>10900</v>
-      </c>
-      <c r="K52" s="3">
-        <v>12200</v>
-      </c>
-      <c r="L52" s="3">
-        <v>13200</v>
-      </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>16600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>16000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>18500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>15400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>18200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>19200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>13600</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3715,8 +3835,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3789,62 +3912,65 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>374100</v>
+      </c>
+      <c r="E54" s="3">
         <v>362000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>354700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>350200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>345600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>336300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>324300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>332300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>323900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>314300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>287000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>286500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>259700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>251600</v>
-      </c>
-      <c r="Q54" s="3">
-        <v>253400</v>
       </c>
       <c r="R54" s="3">
         <v>253400</v>
       </c>
       <c r="S54" s="3">
+        <v>253400</v>
+      </c>
+      <c r="T54" s="3">
         <v>251500</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3863,8 +3989,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3891,8 +4020,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3919,62 +4049,63 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E57" s="3">
         <v>11900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>12300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4400</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3993,31 +4124,34 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>9900</v>
+        <v>11400</v>
       </c>
       <c r="E58" s="3">
-        <v>8900</v>
+        <v>10400</v>
       </c>
       <c r="F58" s="3">
-        <v>7900</v>
+        <v>9300</v>
       </c>
       <c r="G58" s="3">
-        <v>7900</v>
+        <v>8300</v>
       </c>
       <c r="H58" s="3">
-        <v>7900</v>
+        <v>8300</v>
       </c>
       <c r="I58" s="3">
-        <v>8000</v>
+        <v>8400</v>
       </c>
       <c r="J58" s="3">
-        <v>7900</v>
+        <v>8400</v>
       </c>
       <c r="K58" s="3">
         <v>7900</v>
@@ -4026,29 +4160,29 @@
         <v>7900</v>
       </c>
       <c r="M58" s="3">
-        <v>7800</v>
+        <v>7900</v>
       </c>
       <c r="N58" s="3">
         <v>7800</v>
       </c>
       <c r="O58" s="3">
-        <v>9600</v>
+        <v>7800</v>
       </c>
       <c r="P58" s="3">
         <v>9600</v>
       </c>
       <c r="Q58" s="3">
-        <v>9500</v>
+        <v>9600</v>
       </c>
       <c r="R58" s="3">
         <v>9500</v>
       </c>
       <c r="S58" s="3">
+        <v>9500</v>
+      </c>
+      <c r="T58" s="3">
         <v>9400</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4067,62 +4201,65 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>21100</v>
-      </c>
-      <c r="E59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3">
+        <v>300</v>
+      </c>
+      <c r="H59" s="3">
+        <v>600</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3">
+        <v>900</v>
+      </c>
+      <c r="K59" s="3">
+        <v>15900</v>
+      </c>
+      <c r="L59" s="3">
+        <v>19100</v>
+      </c>
+      <c r="M59" s="3">
+        <v>19900</v>
+      </c>
+      <c r="N59" s="3">
+        <v>13200</v>
+      </c>
+      <c r="O59" s="3">
+        <v>11800</v>
+      </c>
+      <c r="P59" s="3">
+        <v>13600</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>14200</v>
+      </c>
+      <c r="R59" s="3">
+        <v>11000</v>
+      </c>
+      <c r="S59" s="3">
+        <v>13000</v>
+      </c>
+      <c r="T59" s="3">
         <v>12600</v>
       </c>
-      <c r="F59" s="3">
-        <v>13500</v>
-      </c>
-      <c r="G59" s="3">
-        <v>16200</v>
-      </c>
-      <c r="H59" s="3">
-        <v>22000</v>
-      </c>
-      <c r="I59" s="3">
-        <v>12700</v>
-      </c>
-      <c r="J59" s="3">
-        <v>15900</v>
-      </c>
-      <c r="K59" s="3">
-        <v>19100</v>
-      </c>
-      <c r="L59" s="3">
-        <v>19900</v>
-      </c>
-      <c r="M59" s="3">
-        <v>13200</v>
-      </c>
-      <c r="N59" s="3">
-        <v>11800</v>
-      </c>
-      <c r="O59" s="3">
-        <v>13600</v>
-      </c>
-      <c r="P59" s="3">
-        <v>14200</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>11000</v>
-      </c>
-      <c r="R59" s="3">
-        <v>13000</v>
-      </c>
-      <c r="S59" s="3">
-        <v>12600</v>
-      </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4141,62 +4278,65 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>38900</v>
+      </c>
+      <c r="E60" s="3">
         <v>42900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>33800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>29400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>30200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>35000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>23900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>28400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>30300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>32300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>26100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>24600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>29000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>29100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>26000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>28500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>26400</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4215,62 +4355,65 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>49800</v>
+        <v>50600</v>
       </c>
       <c r="E61" s="3">
-        <v>52700</v>
+        <v>53700</v>
       </c>
       <c r="F61" s="3">
-        <v>55600</v>
+        <v>56700</v>
       </c>
       <c r="G61" s="3">
-        <v>57600</v>
+        <v>59800</v>
       </c>
       <c r="H61" s="3">
-        <v>59600</v>
+        <v>61800</v>
       </c>
       <c r="I61" s="3">
-        <v>61500</v>
+        <v>63800</v>
       </c>
       <c r="J61" s="3">
+        <v>65900</v>
+      </c>
+      <c r="K61" s="3">
         <v>63500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>65500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>67500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>69400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>71400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>49000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>51400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>53900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>56300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>58700</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4289,62 +4432,65 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>14000</v>
+        <v>9300</v>
       </c>
       <c r="E62" s="3">
-        <v>13900</v>
+        <v>10000</v>
       </c>
       <c r="F62" s="3">
-        <v>15000</v>
+        <v>9900</v>
       </c>
       <c r="G62" s="3">
-        <v>14600</v>
+        <v>10900</v>
       </c>
       <c r="H62" s="3">
-        <v>14000</v>
+        <v>10300</v>
       </c>
       <c r="I62" s="3">
-        <v>13900</v>
+        <v>9700</v>
       </c>
       <c r="J62" s="3">
+        <v>9600</v>
+      </c>
+      <c r="K62" s="3">
         <v>13300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>8500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>8700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>9000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>9600</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4363,8 +4509,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4437,8 +4586,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4511,8 +4663,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4585,62 +4740,65 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>98800</v>
+      </c>
+      <c r="E66" s="3">
         <v>106700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>100400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>100000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>102400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>108500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>99300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>105200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>105100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>109400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>103600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>104200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>85700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>89000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>88600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>93700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>94700</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4659,8 +4817,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4687,8 +4848,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4761,8 +4923,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4835,8 +5000,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4909,8 +5077,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4983,56 +5154,59 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>63800</v>
+      </c>
+      <c r="E72" s="3">
         <v>46800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>47500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>45600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>40800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>27900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>26900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>30700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>24700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>13500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-5600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-4500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-10000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-18900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-14300</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5048,8 +5222,8 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X72" s="3">
-        <v>0</v>
+      <c r="X72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y72" s="3">
         <v>0</v>
@@ -5057,8 +5231,11 @@
       <c r="Z72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5131,8 +5308,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5205,8 +5385,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5279,62 +5462,65 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>275300</v>
+      </c>
+      <c r="E76" s="3">
         <v>255300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>254300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>250200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>243200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>227800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>225100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>227100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>218800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>204900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>183400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>182300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>174100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>162600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>164700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>159600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>156900</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5353,8 +5539,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5427,73 +5616,76 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5506,68 +5698,71 @@
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>12900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>6000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>11200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>19200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>8900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-14300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>5400</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5580,8 +5775,11 @@
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5608,46 +5806,47 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>5800</v>
+        <v>5000</v>
       </c>
       <c r="E83" s="3">
-        <v>5400</v>
+        <v>4900</v>
       </c>
       <c r="F83" s="3">
-        <v>5400</v>
+        <v>4800</v>
       </c>
       <c r="G83" s="3">
-        <v>5300</v>
+        <v>4900</v>
       </c>
       <c r="H83" s="3">
-        <v>5300</v>
+        <v>4800</v>
       </c>
       <c r="I83" s="3">
-        <v>5200</v>
+        <v>4800</v>
       </c>
       <c r="J83" s="3">
-        <v>5200</v>
+        <v>4800</v>
       </c>
       <c r="K83" s="3">
         <v>5200</v>
       </c>
       <c r="L83" s="3">
+        <v>5200</v>
+      </c>
+      <c r="M83" s="3">
         <v>5100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5800</v>
-      </c>
-      <c r="O83" s="3">
-        <v>5700</v>
       </c>
       <c r="P83" s="3">
         <v>5700</v>
@@ -5656,20 +5855,20 @@
         <v>5700</v>
       </c>
       <c r="R83" s="3">
+        <v>5700</v>
+      </c>
+      <c r="S83" s="3">
         <v>6000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>16100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>5000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>14800</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5682,8 +5881,11 @@
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5756,8 +5958,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5830,8 +6035,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5904,8 +6112,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5978,8 +6189,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6052,68 +6266,71 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E89" s="3">
         <v>200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>14300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>21500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>13500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>17900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-11800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>21300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>33000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>17200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>9600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>21600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>10100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>7800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>6700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>21900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>6200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>21700</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6126,8 +6343,11 @@
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6154,68 +6374,69 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-18800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-22000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-17700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-15800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-16300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-13300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-9500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-14200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-11600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-33600</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6228,8 +6449,11 @@
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6302,8 +6526,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6376,68 +6603,71 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-18800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-22800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-17700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-15800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-16300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-13300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-8100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-13100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-12500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-32100</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6450,8 +6680,11 @@
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6478,31 +6711,32 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6552,8 +6786,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6626,8 +6863,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6700,8 +6940,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6774,22 +7017,25 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3300</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-2000</v>
       </c>
       <c r="H100" s="3">
         <v>-2000</v>
@@ -6798,44 +7044,44 @@
         <v>-2000</v>
       </c>
       <c r="J100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="K100" s="3">
         <v>-2200</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-2000</v>
       </c>
       <c r="L100" s="3">
         <v>-2000</v>
       </c>
       <c r="M100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="N100" s="3">
         <v>-2100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>18500</v>
-      </c>
-      <c r="O100" s="3">
-        <v>-2500</v>
       </c>
       <c r="P100" s="3">
         <v>-2500</v>
       </c>
       <c r="Q100" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="R100" s="3">
         <v>-4900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>13500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-41000</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6848,31 +7094,34 @@
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6922,68 +7171,71 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-21000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-10500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-27100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>9600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>23500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>12400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>6500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>32000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>4700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>9900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>6800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-51400</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6994,6 +7246,9 @@
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MNTK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MNTK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="92">
   <si>
     <t>MNTK</t>
   </si>
@@ -656,103 +656,103 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
@@ -765,71 +765,74 @@
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>27700</v>
+      </c>
+      <c r="E8" s="3">
         <v>65900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>43300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>38800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>46800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>55700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>53300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>19200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>49600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>55900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>67900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>32200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>45300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>39700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>31700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>31400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>24800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>75600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>22000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>83700</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
@@ -842,71 +845,74 @@
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E9" s="3">
         <v>26600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>27700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>21000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>25400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>25700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>25400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>18100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>24700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>26300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>30000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>20400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>22400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>19800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>19200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>16800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>16100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>45700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>12200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>46500</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
@@ -919,71 +925,74 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E10" s="3">
         <v>39300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>15600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>17800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>21400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>30000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>27800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>24900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>29600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>37900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>11800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>22900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>19900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>12500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>14600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>8700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>29900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>9800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>37200</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
@@ -996,8 +1005,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1025,8 +1037,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1102,8 +1115,11 @@
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1179,71 +1195,74 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E14" s="3">
         <v>3400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2300</v>
-      </c>
-      <c r="M14" s="3">
-        <v>100</v>
       </c>
       <c r="N14" s="3">
         <v>100</v>
       </c>
       <c r="O14" s="3">
+        <v>100</v>
+      </c>
+      <c r="P14" s="3">
         <v>700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>200</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>600</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1600</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1256,31 +1275,34 @@
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E15" s="3">
         <v>6000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>5800</v>
-      </c>
-      <c r="F15" s="3">
-        <v>5400</v>
       </c>
       <c r="G15" s="3">
         <v>5400</v>
       </c>
       <c r="H15" s="3">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="I15" s="3">
         <v>5300</v>
       </c>
       <c r="J15" s="3">
-        <v>5200</v>
+        <v>5300</v>
       </c>
       <c r="K15" s="3">
         <v>5200</v>
@@ -1289,16 +1311,16 @@
         <v>5200</v>
       </c>
       <c r="M15" s="3">
+        <v>5200</v>
+      </c>
+      <c r="N15" s="3">
         <v>5100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>5200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>5800</v>
-      </c>
-      <c r="P15" s="3">
-        <v>5700</v>
       </c>
       <c r="Q15" s="3">
         <v>5700</v>
@@ -1307,20 +1329,20 @@
         <v>5700</v>
       </c>
       <c r="S15" s="3">
+        <v>5700</v>
+      </c>
+      <c r="T15" s="3">
         <v>6000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>16100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>5000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>14800</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1333,8 +1355,11 @@
       <c r="AA15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1359,71 +1384,72 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>40100</v>
+      </c>
+      <c r="E17" s="3">
         <v>39800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>42300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>35800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>39100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>38900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>39400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>32800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>41000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>42200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>43900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>33800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>36100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>33000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>32200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>43700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>26900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>69900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>21100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>73600</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1436,71 +1462,74 @@
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="E18" s="3">
         <v>26200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>7700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>16800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>13800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-13600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>8600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>13700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>24000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>9200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-12300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>5700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>10100</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1513,8 +1542,11 @@
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1542,8 +1574,9 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1554,59 +1587,59 @@
         <v>-100</v>
       </c>
       <c r="F20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G20" s="3">
         <v>-1100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-600</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1619,71 +1652,74 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E21" s="3">
         <v>32300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>6900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>9500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>13200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>22400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>19200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-8400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>13900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>18900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>29100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>15000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>11800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-6500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>21500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>25000</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1696,71 +1732,74 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1500</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
         <v>300</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
       <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
         <v>900</v>
-      </c>
-      <c r="P22" s="3">
-        <v>700</v>
       </c>
       <c r="Q22" s="3">
         <v>700</v>
       </c>
       <c r="R22" s="3">
+        <v>700</v>
+      </c>
+      <c r="S22" s="3">
         <v>600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>3500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>5300</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1773,71 +1812,74 @@
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="E23" s="3">
         <v>21000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>15700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>12900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-15800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>13700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>23700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-12900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4900</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1850,71 +1892,74 @@
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E24" s="3">
         <v>4000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>11900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-12100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-5700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-500</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1927,8 +1972,11 @@
       <c r="AA24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2004,71 +2052,74 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E26" s="3">
         <v>17000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>12900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>11200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>19200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>8900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-14300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>5400</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2081,71 +2132,74 @@
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E27" s="3">
         <v>17000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>12900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>11200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>19200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>8900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-14300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>5400</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2158,8 +2212,11 @@
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2235,8 +2292,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2312,8 +2372,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2389,8 +2452,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2466,8 +2532,11 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2478,59 +2547,59 @@
         <v>100</v>
       </c>
       <c r="F32" s="3">
+        <v>100</v>
+      </c>
+      <c r="G32" s="3">
         <v>1100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>600</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2543,71 +2612,74 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E33" s="3">
         <v>17000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>12900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>11200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>19200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>8900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-14300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>5400</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2620,8 +2692,11 @@
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2697,71 +2772,74 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E35" s="3">
         <v>17000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>12900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>11200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>19200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>8900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-14300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>5400</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2774,76 +2852,79 @@
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2856,8 +2937,11 @@
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2885,8 +2969,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2914,65 +2999,66 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>45600</v>
+      </c>
+      <c r="E41" s="3">
         <v>55000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>42300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>63300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>73800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>73300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>77600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>78000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>105200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>95600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>72200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>59800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>53300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>20900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>16400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>22600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>21000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>19500</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2991,16 +3077,19 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>500</v>
+      </c>
+      <c r="E42" s="3">
         <v>400</v>
-      </c>
-      <c r="E42" s="3">
-        <v>800</v>
       </c>
       <c r="F42" s="3">
         <v>800</v>
@@ -3009,17 +3098,17 @@
         <v>800</v>
       </c>
       <c r="H42" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="I42" s="3">
         <v>1000</v>
       </c>
       <c r="J42" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K42" s="3">
         <v>800</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -3068,65 +3157,68 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E43" s="3">
         <v>19200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>22500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>12800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>28200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>23800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>15300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>16200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>21200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>32900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>14500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>18200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>15300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>10100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>8900</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3145,8 +3237,11 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3171,8 +3266,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3222,8 +3317,11 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3248,39 +3346,39 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>3500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5800</v>
-      </c>
-      <c r="N45" s="3">
-        <v>3700</v>
       </c>
       <c r="O45" s="3">
         <v>3700</v>
       </c>
       <c r="P45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="Q45" s="3">
         <v>3200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4600</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3299,65 +3397,68 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>57200</v>
+      </c>
+      <c r="E46" s="3">
         <v>79300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>71100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>76600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>90200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>107400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>108300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>96600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>124900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>121700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>111000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>78000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>75200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>39400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>31000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>31400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>32500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>33000</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3376,49 +3477,52 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>300</v>
+      </c>
+      <c r="E47" s="3">
         <v>200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>600</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P47" s="3">
-        <v>7100</v>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>7100</v>
@@ -3426,8 +3530,8 @@
       <c r="R47" s="3">
         <v>7100</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
+      <c r="S47" s="3">
+        <v>7100</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
@@ -3444,8 +3548,8 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z47" s="3">
         <v>0</v>
@@ -3453,65 +3557,68 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>259500</v>
+      </c>
+      <c r="E48" s="3">
         <v>254000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>248700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>235700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>218600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>210000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>199400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>188500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>180800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>174200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>176400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>178500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>181200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>179700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>184700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>182800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>187600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>190500</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3530,65 +3637,68 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E49" s="3">
         <v>18500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>17900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>18200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>18400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>15000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>15300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>15500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>15800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>15900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>13700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>13900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>14100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>15000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>13400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>13700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>14000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>14500</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3607,8 +3717,11 @@
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3684,8 +3797,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3761,65 +3877,68 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E52" s="3">
         <v>12000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>11600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11700</v>
       </c>
-      <c r="G52" s="3">
-        <v>20500</v>
-      </c>
       <c r="H52" s="3">
+        <v>10300</v>
+      </c>
+      <c r="I52" s="3">
         <v>10100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>8600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>12200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>13200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>16600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>16000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>18500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>15400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>18200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>19200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>13600</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3838,8 +3957,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3915,65 +4037,68 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>349000</v>
+      </c>
+      <c r="E54" s="3">
         <v>374100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>362000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>354700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>350200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>345600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>336300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>324300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>332300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>323900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>314300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>287000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>286500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>259700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>251600</v>
-      </c>
-      <c r="R54" s="3">
-        <v>253400</v>
       </c>
       <c r="S54" s="3">
         <v>253400</v>
       </c>
       <c r="T54" s="3">
+        <v>253400</v>
+      </c>
+      <c r="U54" s="3">
         <v>251500</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3992,8 +4117,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4021,8 +4149,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4050,65 +4179,66 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E57" s="3">
         <v>10200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>12300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4400</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4127,34 +4257,37 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E58" s="3">
         <v>11400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>9300</v>
-      </c>
-      <c r="G58" s="3">
-        <v>8300</v>
       </c>
       <c r="H58" s="3">
         <v>8300</v>
       </c>
       <c r="I58" s="3">
-        <v>8400</v>
+        <v>8300</v>
       </c>
       <c r="J58" s="3">
         <v>8400</v>
       </c>
       <c r="K58" s="3">
-        <v>7900</v>
+        <v>8400</v>
       </c>
       <c r="L58" s="3">
         <v>7900</v>
@@ -4163,29 +4296,29 @@
         <v>7900</v>
       </c>
       <c r="N58" s="3">
-        <v>7800</v>
+        <v>7900</v>
       </c>
       <c r="O58" s="3">
         <v>7800</v>
       </c>
       <c r="P58" s="3">
-        <v>9600</v>
+        <v>7800</v>
       </c>
       <c r="Q58" s="3">
         <v>9600</v>
       </c>
       <c r="R58" s="3">
-        <v>9500</v>
+        <v>9600</v>
       </c>
       <c r="S58" s="3">
         <v>9500</v>
       </c>
       <c r="T58" s="3">
+        <v>9500</v>
+      </c>
+      <c r="U58" s="3">
         <v>9400</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4204,65 +4337,68 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>600</v>
+      </c>
+      <c r="E59" s="3">
         <v>1600</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3">
         <v>300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>600</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K59" s="3">
         <v>900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>15900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>19100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>19900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>13600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>14200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>13000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>12600</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4281,65 +4417,68 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>33500</v>
+      </c>
+      <c r="E60" s="3">
         <v>38900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>42900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>33800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>29400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>30200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>35000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>23900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>28400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>30300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>32300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>26100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>24600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>29000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>29100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>26000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>28500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>26400</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4358,65 +4497,68 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>48900</v>
+      </c>
+      <c r="E61" s="3">
         <v>50600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>53700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>56700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>59800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>61800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>63800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>65900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>63500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>65500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>67500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>69400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>71400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>49000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>51400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>53900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>56300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>58700</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4435,65 +4577,68 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E62" s="3">
         <v>9300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>10000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>10300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>13300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>9500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>8200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>8500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>8700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>9000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>9600</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4512,8 +4657,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4589,8 +4737,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4666,8 +4817,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4743,65 +4897,68 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>91600</v>
+      </c>
+      <c r="E66" s="3">
         <v>98800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>106700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>100400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>100000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>102400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>108500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>99300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>105200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>105100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>109400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>103600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>104200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>85700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>89000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>88600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>93700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>94700</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4820,8 +4977,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4849,8 +5009,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4926,8 +5087,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5003,8 +5167,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5080,8 +5247,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5157,59 +5327,62 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>55300</v>
+      </c>
+      <c r="E72" s="3">
         <v>63800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>46800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>47500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>45600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>40800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>27900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>26900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>30700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>24700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>13500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-5600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-4500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-18900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-14300</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5225,8 +5398,8 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y72" s="3">
-        <v>0</v>
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z72" s="3">
         <v>0</v>
@@ -5234,8 +5407,11 @@
       <c r="AA72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5311,8 +5487,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5388,8 +5567,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5465,65 +5647,68 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>257400</v>
+      </c>
+      <c r="E76" s="3">
         <v>275300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>255300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>254300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>250200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>243200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>227800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>225100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>227100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>218800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>204900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>183400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>182300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>174100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>162600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>164700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>159600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>156900</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5542,8 +5727,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5619,76 +5807,79 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5701,71 +5892,74 @@
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E81" s="3">
         <v>17000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>12900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>11200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>19200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>8900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-14300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>5400</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5778,8 +5972,11 @@
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5807,8 +6004,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5816,16 +6014,16 @@
         <v>5000</v>
       </c>
       <c r="E83" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F83" s="3">
         <v>4900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4900</v>
-      </c>
-      <c r="H83" s="3">
-        <v>4800</v>
       </c>
       <c r="I83" s="3">
         <v>4800</v>
@@ -5834,22 +6032,22 @@
         <v>4800</v>
       </c>
       <c r="K83" s="3">
-        <v>5200</v>
+        <v>4800</v>
       </c>
       <c r="L83" s="3">
         <v>5200</v>
       </c>
       <c r="M83" s="3">
+        <v>5200</v>
+      </c>
+      <c r="N83" s="3">
         <v>5100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5800</v>
-      </c>
-      <c r="P83" s="3">
-        <v>5700</v>
       </c>
       <c r="Q83" s="3">
         <v>5700</v>
@@ -5858,20 +6056,20 @@
         <v>5700</v>
       </c>
       <c r="S83" s="3">
+        <v>5700</v>
+      </c>
+      <c r="T83" s="3">
         <v>6000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>16100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>5000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>14800</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5884,8 +6082,11 @@
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5961,8 +6162,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6038,8 +6242,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6115,8 +6322,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6192,8 +6402,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6269,71 +6482,74 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>700</v>
+      </c>
+      <c r="E89" s="3">
         <v>28600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>14300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>21500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>13500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>17900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-11800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>21300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>33000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>17200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>9600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>21600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>10100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>7800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>6700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>21900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>6200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>21700</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6346,8 +6562,11 @@
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6375,71 +6594,72 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-12600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-18800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-22000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-17700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-15800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-16300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-13300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-9500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-14200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-11600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-33600</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6452,8 +6672,11 @@
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6529,8 +6752,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6606,71 +6832,74 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-12600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-18800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-22800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-17700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-15800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-16300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-13300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-8100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-7300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-13100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-12500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-32100</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6683,8 +6912,11 @@
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6712,8 +6944,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6738,8 +6971,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6789,8 +7022,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6866,8 +7102,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6943,8 +7182,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7020,25 +7262,28 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3300</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-2000</v>
       </c>
       <c r="I100" s="3">
         <v>-2000</v>
@@ -7047,44 +7292,44 @@
         <v>-2000</v>
       </c>
       <c r="K100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="L100" s="3">
         <v>-2200</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-2000</v>
       </c>
       <c r="M100" s="3">
         <v>-2000</v>
       </c>
       <c r="N100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="O100" s="3">
         <v>-2100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>18500</v>
-      </c>
-      <c r="P100" s="3">
-        <v>-2500</v>
       </c>
       <c r="Q100" s="3">
         <v>-2500</v>
       </c>
       <c r="R100" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="S100" s="3">
         <v>-4900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>13500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-41000</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7097,8 +7342,11 @@
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7123,8 +7371,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -7174,71 +7422,74 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E102" s="3">
         <v>12700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-21000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-10500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-27100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>9600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>23500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>12400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>6500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>32000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>4700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-6300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>9900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>6800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-51400</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7249,6 +7500,9 @@
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MNTK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MNTK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="92">
   <si>
     <t>MNTK</t>
   </si>
@@ -656,106 +656,107 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
@@ -768,74 +769,77 @@
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>42600</v>
+      </c>
+      <c r="E8" s="3">
         <v>27700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>65900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>43300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>38800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>46800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>55700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>53300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>19200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>49600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>55900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>67900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>32200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>45300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>39700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>31700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>31400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>24800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>75600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>22000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>83700</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
@@ -848,74 +852,77 @@
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>25100</v>
+      </c>
+      <c r="E9" s="3">
         <v>22900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>26600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>27700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>21000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>25400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>25700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>25400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>18100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>24700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>26300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>30000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>20400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>22400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>19800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>19200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>16800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>16100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>45700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>12200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>46500</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
@@ -928,74 +935,77 @@
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E10" s="3">
         <v>4800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>39300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>15600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>17800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>21400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>30000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>27800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>24900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>29600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>37900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>11800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>22900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>19900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>12500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>14600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>8700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>29900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>9800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>37200</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1008,8 +1018,11 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1038,8 +1051,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1118,8 +1132,11 @@
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1198,74 +1215,77 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E14" s="3">
         <v>-2600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2300</v>
-      </c>
-      <c r="N14" s="3">
-        <v>100</v>
       </c>
       <c r="O14" s="3">
         <v>100</v>
       </c>
       <c r="P14" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q14" s="3">
         <v>700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>200</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>600</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1600</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1278,34 +1298,37 @@
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E15" s="3">
         <v>6200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>6000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>5800</v>
-      </c>
-      <c r="G15" s="3">
-        <v>5400</v>
       </c>
       <c r="H15" s="3">
         <v>5400</v>
       </c>
       <c r="I15" s="3">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="J15" s="3">
         <v>5300</v>
       </c>
       <c r="K15" s="3">
-        <v>5200</v>
+        <v>5300</v>
       </c>
       <c r="L15" s="3">
         <v>5200</v>
@@ -1314,16 +1337,16 @@
         <v>5200</v>
       </c>
       <c r="N15" s="3">
+        <v>5200</v>
+      </c>
+      <c r="O15" s="3">
         <v>5100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>5200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>5800</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>5700</v>
       </c>
       <c r="R15" s="3">
         <v>5700</v>
@@ -1332,20 +1355,20 @@
         <v>5700</v>
       </c>
       <c r="T15" s="3">
+        <v>5700</v>
+      </c>
+      <c r="U15" s="3">
         <v>6000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>16100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>5000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>14800</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1358,8 +1381,11 @@
       <c r="AB15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1385,74 +1411,75 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>38600</v>
+      </c>
+      <c r="E17" s="3">
         <v>40100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>39800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>42300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>35800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>39100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>38900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>39400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>32800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>41000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>42200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>43900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>33800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>36100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>33000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>32200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>43700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>26900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>69900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>21100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>73600</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1465,74 +1492,77 @@
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-12400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>26200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>7700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>16800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>13800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-13600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>8600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>13700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>24000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>9200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>6700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-12300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>5700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>10100</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1545,8 +1575,11 @@
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1575,8 +1608,9 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1590,59 +1624,59 @@
         <v>-100</v>
       </c>
       <c r="G20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H20" s="3">
         <v>-1100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-600</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1655,74 +1689,77 @@
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-6100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>32300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>6900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>9500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>13200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>22400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>19200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-8400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>13900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>18900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>29100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>15000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>11800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-6500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>21500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>5800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>25000</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1735,74 +1772,77 @@
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E22" s="3">
         <v>1000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1500</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
         <v>300</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
       <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
         <v>900</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>700</v>
       </c>
       <c r="R22" s="3">
         <v>700</v>
       </c>
       <c r="S22" s="3">
+        <v>700</v>
+      </c>
+      <c r="T22" s="3">
         <v>600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>3500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>5300</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1815,74 +1855,77 @@
       <c r="AB22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-10700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>21000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>15700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>12900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-15800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>13700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>23700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>8400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-12900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4900</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1895,74 +1938,77 @@
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E24" s="3">
         <v>-2300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>11900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-12100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-3500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-5700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-500</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1975,8 +2021,11 @@
       <c r="AB24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2055,74 +2104,77 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-8500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>17000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>12900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>11200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>19200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>8900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-14300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>5400</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2135,74 +2187,77 @@
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-8500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>17000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>12900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>11200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>19200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>8900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-14300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>5400</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2215,8 +2270,11 @@
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2295,8 +2353,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2375,8 +2436,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2455,8 +2519,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2535,8 +2602,11 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2550,59 +2620,59 @@
         <v>100</v>
       </c>
       <c r="G32" s="3">
+        <v>100</v>
+      </c>
+      <c r="H32" s="3">
         <v>1100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>600</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2615,74 +2685,77 @@
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-8500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>17000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>12900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>11200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>19200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>8900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-14300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>5400</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2695,8 +2768,11 @@
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2775,74 +2851,77 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-8500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>17000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>12900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>11200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>19200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>8900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-14300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>5400</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2855,79 +2934,82 @@
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2940,8 +3022,11 @@
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2970,8 +3055,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3000,68 +3086,69 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>40100</v>
+      </c>
+      <c r="E41" s="3">
         <v>45600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>55000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>42300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>63300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>73800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>73300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>77600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>78000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>105200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>95600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>72200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>59800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>53300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>20900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>16400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>22600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>21000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>19500</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3080,19 +3167,22 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>400</v>
+      </c>
+      <c r="E42" s="3">
         <v>500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>400</v>
-      </c>
-      <c r="F42" s="3">
-        <v>800</v>
       </c>
       <c r="G42" s="3">
         <v>800</v>
@@ -3101,17 +3191,17 @@
         <v>800</v>
       </c>
       <c r="I42" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="J42" s="3">
         <v>1000</v>
       </c>
       <c r="K42" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L42" s="3">
         <v>800</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -3160,68 +3250,71 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E43" s="3">
         <v>8200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>19200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>22500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>28200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>23800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>15300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>16200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>21200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>32900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>14500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>18200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>15300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>10100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>8900</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3240,8 +3333,11 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3269,8 +3365,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3320,8 +3416,11 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3349,39 +3448,39 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>3500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5800</v>
-      </c>
-      <c r="O45" s="3">
-        <v>3700</v>
       </c>
       <c r="P45" s="3">
         <v>3700</v>
       </c>
       <c r="Q45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="R45" s="3">
         <v>3200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4600</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3400,68 +3499,71 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>52200</v>
+      </c>
+      <c r="E46" s="3">
         <v>57200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>79300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>71100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>76600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>90200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>107400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>108300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>96600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>124900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>121700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>111000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>78000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>75200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>39400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>31000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>31400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>32500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>33000</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3480,52 +3582,55 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>200</v>
+      </c>
+      <c r="E47" s="3">
         <v>300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>600</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>7100</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>7100</v>
@@ -3533,8 +3638,8 @@
       <c r="S47" s="3">
         <v>7100</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
+      <c r="T47" s="3">
+        <v>7100</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
@@ -3551,8 +3656,8 @@
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z47" s="3">
-        <v>0</v>
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA47" s="3">
         <v>0</v>
@@ -3560,68 +3665,71 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>266900</v>
+      </c>
+      <c r="E48" s="3">
         <v>259500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>254000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>248700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>235700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>218600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>210000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>199400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>188500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>180800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>174200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>176400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>178500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>181200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>179700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>184700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>182800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>187600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>190500</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3640,68 +3748,71 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E49" s="3">
         <v>18100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>18500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>17900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>18200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>18400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>15000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>15300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>15500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>15800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>15900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>13700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>13900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>14100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>15000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>13400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>13700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>14000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>14500</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3720,8 +3831,11 @@
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3800,8 +3914,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3880,68 +3997,71 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E52" s="3">
         <v>12600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>10300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>10100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>12200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>13200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>16600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>16000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>18500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>15400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>18200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>19200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>13600</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3960,8 +4080,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4040,68 +4163,71 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>354200</v>
+      </c>
+      <c r="E54" s="3">
         <v>349000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>374100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>362000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>354700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>350200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>345600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>336300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>324300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>332300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>323900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>314300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>287000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>286500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>259700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>251600</v>
-      </c>
-      <c r="S54" s="3">
-        <v>253400</v>
       </c>
       <c r="T54" s="3">
         <v>253400</v>
       </c>
       <c r="U54" s="3">
+        <v>253400</v>
+      </c>
+      <c r="V54" s="3">
         <v>251500</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4120,8 +4246,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4150,8 +4279,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4180,68 +4310,69 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E57" s="3">
         <v>8900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>12300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4400</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4260,37 +4391,40 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E58" s="3">
         <v>14000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>10400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>9300</v>
-      </c>
-      <c r="H58" s="3">
-        <v>8300</v>
       </c>
       <c r="I58" s="3">
         <v>8300</v>
       </c>
       <c r="J58" s="3">
-        <v>8400</v>
+        <v>8300</v>
       </c>
       <c r="K58" s="3">
         <v>8400</v>
       </c>
       <c r="L58" s="3">
-        <v>7900</v>
+        <v>8400</v>
       </c>
       <c r="M58" s="3">
         <v>7900</v>
@@ -4299,29 +4433,29 @@
         <v>7900</v>
       </c>
       <c r="O58" s="3">
-        <v>7800</v>
+        <v>7900</v>
       </c>
       <c r="P58" s="3">
         <v>7800</v>
       </c>
       <c r="Q58" s="3">
-        <v>9600</v>
+        <v>7800</v>
       </c>
       <c r="R58" s="3">
         <v>9600</v>
       </c>
       <c r="S58" s="3">
-        <v>9500</v>
+        <v>9600</v>
       </c>
       <c r="T58" s="3">
         <v>9500</v>
       </c>
       <c r="U58" s="3">
+        <v>9500</v>
+      </c>
+      <c r="V58" s="3">
         <v>9400</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4340,68 +4474,71 @@
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3">
         <v>600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1600</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3">
         <v>300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>600</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3">
         <v>900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>15900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>19100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>19900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>13200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>13600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>14200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>11000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>13000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>12600</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4420,68 +4557,71 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E60" s="3">
         <v>33500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>38900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>42900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>33800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>29400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>30200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>35000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>23900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>28400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>30300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>32300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>26100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>24600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>29000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>29100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>26000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>28500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>26400</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4500,68 +4640,71 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>45600</v>
+      </c>
+      <c r="E61" s="3">
         <v>48900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>50600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>53700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>56700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>59800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>61800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>63800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>65900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>63500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>65500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>67500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>69400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>71400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>49000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>51400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>53900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>56300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>58700</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4580,68 +4723,71 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E62" s="3">
         <v>9100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>9900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>10900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>13300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>9300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>9500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>8000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>8200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>8500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>8700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>9000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>9600</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4660,8 +4806,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4740,8 +4889,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4820,8 +4972,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4900,68 +5055,71 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>96000</v>
+      </c>
+      <c r="E66" s="3">
         <v>91600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>98800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>106700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>100400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>100000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>102400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>108500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>99300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>105200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>105100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>109400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>103600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>104200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>85700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>89000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>88600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>93700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>94700</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4980,8 +5138,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5010,8 +5171,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5090,8 +5252,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5170,8 +5335,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5250,8 +5418,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5330,62 +5501,65 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>54900</v>
+      </c>
+      <c r="E72" s="3">
         <v>55300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>63800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>46800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>47500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>45600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>40800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>27900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>26900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>30700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>24700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>13500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-5600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-10000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-18900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-14300</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5401,8 +5575,8 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z72" s="3">
-        <v>0</v>
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA72" s="3">
         <v>0</v>
@@ -5410,8 +5584,11 @@
       <c r="AB72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5490,8 +5667,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5570,8 +5750,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5650,68 +5833,71 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>258200</v>
+      </c>
+      <c r="E76" s="3">
         <v>257400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>275300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>255300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>254300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>250200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>243200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>227800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>225100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>227100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>218800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>204900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>183400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>182300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>174100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>162600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>164700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>159600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>156900</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5730,8 +5916,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5810,79 +5999,82 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5895,74 +6087,77 @@
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-8500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>17000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>12900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>11200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>19200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>8900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-14300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>5400</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5975,8 +6170,11 @@
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6005,28 +6203,29 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="E83" s="3">
         <v>5000</v>
       </c>
       <c r="F83" s="3">
+        <v>5000</v>
+      </c>
+      <c r="G83" s="3">
         <v>4900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4900</v>
-      </c>
-      <c r="I83" s="3">
-        <v>4800</v>
       </c>
       <c r="J83" s="3">
         <v>4800</v>
@@ -6035,22 +6234,22 @@
         <v>4800</v>
       </c>
       <c r="L83" s="3">
-        <v>5200</v>
+        <v>4800</v>
       </c>
       <c r="M83" s="3">
         <v>5200</v>
       </c>
       <c r="N83" s="3">
+        <v>5200</v>
+      </c>
+      <c r="O83" s="3">
         <v>5100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5800</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>5700</v>
       </c>
       <c r="R83" s="3">
         <v>5700</v>
@@ -6059,20 +6258,20 @@
         <v>5700</v>
       </c>
       <c r="T83" s="3">
+        <v>5700</v>
+      </c>
+      <c r="U83" s="3">
         <v>6000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>16100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>5000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>14800</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6085,8 +6284,11 @@
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6165,8 +6367,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6245,8 +6450,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6325,8 +6533,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6405,8 +6616,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6485,74 +6699,77 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E89" s="3">
         <v>700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>28600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>14300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>21500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>13500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>17900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-11800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>21300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>33000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>17200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>9600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>21600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>10100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>7800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>6700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>21900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>6200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>21700</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6565,8 +6782,11 @@
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6595,74 +6815,75 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-9800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-12600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-18800</v>
       </c>
-      <c r="G91" s="3">
-        <v>-22000</v>
-      </c>
       <c r="H91" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="I91" s="3">
         <v>-17700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-15800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-16300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-13300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-9500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-14200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-11600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-33600</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6675,8 +6896,11 @@
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6755,8 +6979,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6835,74 +7062,77 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-8100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-12600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-18800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-22800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-17700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-15800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-16300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-13300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-7500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-7300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-13100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-12500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-32100</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6915,8 +7145,11 @@
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6945,8 +7178,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6974,8 +7208,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7025,8 +7259,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7105,8 +7342,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7185,8 +7425,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7265,28 +7508,31 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3300</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-2000</v>
       </c>
       <c r="J100" s="3">
         <v>-2000</v>
@@ -7295,44 +7541,44 @@
         <v>-2000</v>
       </c>
       <c r="L100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="M100" s="3">
         <v>-2200</v>
-      </c>
-      <c r="M100" s="3">
-        <v>-2000</v>
       </c>
       <c r="N100" s="3">
         <v>-2000</v>
       </c>
       <c r="O100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="P100" s="3">
         <v>-2100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>18500</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>-2500</v>
       </c>
       <c r="R100" s="3">
         <v>-2500</v>
       </c>
       <c r="S100" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="T100" s="3">
         <v>-4900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>13500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-41000</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7345,8 +7591,11 @@
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7374,8 +7623,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -7425,74 +7674,77 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-9400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>12700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-21000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-10500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-27100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>9600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>23500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>12400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>6500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>32000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>4700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-6300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>9900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>6800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-51400</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7503,6 +7755,9 @@
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MNTK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MNTK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="92">
   <si>
     <t>MNTK</t>
   </si>
@@ -656,110 +656,111 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
@@ -772,77 +773,80 @@
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>45100</v>
+      </c>
+      <c r="E8" s="3">
         <v>42600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>27700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>65900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>43300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>38800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>46800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>55700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>53300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>19200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>49600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>55900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>67900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>32200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>45300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>39700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>31700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>31400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>24800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>75600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>22000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>83700</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
@@ -855,77 +859,80 @@
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E9" s="3">
         <v>25100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>22900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>26600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>27700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>21000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>25400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>25700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>25400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>18100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>24700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>26300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>30000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>20400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>22400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>19800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>19200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>16800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>16100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>45700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>12200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>46500</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
@@ -938,77 +945,80 @@
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E10" s="3">
         <v>17500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>39300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>15600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>17800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>21400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>30000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>27800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>24900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>29600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>37900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>11800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>22900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>19900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>12500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>14600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>8700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>29900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>9800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>37200</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1021,8 +1031,11 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1052,8 +1065,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1135,8 +1149,11 @@
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1218,77 +1235,80 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>400</v>
+      </c>
+      <c r="E14" s="3">
         <v>3600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-2600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2300</v>
-      </c>
-      <c r="O14" s="3">
-        <v>100</v>
       </c>
       <c r="P14" s="3">
         <v>100</v>
       </c>
       <c r="Q14" s="3">
+        <v>100</v>
+      </c>
+      <c r="R14" s="3">
         <v>700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>200</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>600</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1600</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1301,37 +1321,40 @@
       <c r="AC14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E15" s="3">
         <v>6300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>6200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>6000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5800</v>
-      </c>
-      <c r="H15" s="3">
-        <v>5400</v>
       </c>
       <c r="I15" s="3">
         <v>5400</v>
       </c>
       <c r="J15" s="3">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="K15" s="3">
         <v>5300</v>
       </c>
       <c r="L15" s="3">
-        <v>5200</v>
+        <v>5300</v>
       </c>
       <c r="M15" s="3">
         <v>5200</v>
@@ -1340,16 +1363,16 @@
         <v>5200</v>
       </c>
       <c r="O15" s="3">
+        <v>5200</v>
+      </c>
+      <c r="P15" s="3">
         <v>5100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>5200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>5800</v>
-      </c>
-      <c r="R15" s="3">
-        <v>5700</v>
       </c>
       <c r="S15" s="3">
         <v>5700</v>
@@ -1358,20 +1381,20 @@
         <v>5700</v>
       </c>
       <c r="U15" s="3">
+        <v>5700</v>
+      </c>
+      <c r="V15" s="3">
         <v>6000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>16100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>5000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>14800</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1384,8 +1407,11 @@
       <c r="AC15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1412,77 +1438,78 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>47100</v>
+      </c>
+      <c r="E17" s="3">
         <v>38600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>40100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>39800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>42300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>35800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>39100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>38900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>39400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>32800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>41000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>42200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>43900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>33800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>36100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>33000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>32200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>43700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>26900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>69900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>21100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>73600</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1495,77 +1522,80 @@
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E18" s="3">
         <v>4000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-12400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>26200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>7700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>16800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>13800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-13600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>8600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>13700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>24000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>9200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>6700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-12300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>5700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>10100</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1578,8 +1608,11 @@
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1609,13 +1642,14 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
         <v>-100</v>
@@ -1627,59 +1661,59 @@
         <v>-100</v>
       </c>
       <c r="H20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I20" s="3">
         <v>-1100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>300</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-600</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1692,77 +1726,80 @@
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E21" s="3">
         <v>10300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-6100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>32300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>6900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>9500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>13200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>22400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>19200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-8400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>13900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>18900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>29100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>15000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>11800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-6500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>21500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>5800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>25000</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1775,8 +1812,11 @@
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1784,68 +1824,68 @@
         <v>1200</v>
       </c>
       <c r="E22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F22" s="3">
         <v>1000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1500</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
       <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
         <v>300</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
         <v>900</v>
-      </c>
-      <c r="R22" s="3">
-        <v>700</v>
       </c>
       <c r="S22" s="3">
         <v>700</v>
       </c>
       <c r="T22" s="3">
+        <v>700</v>
+      </c>
+      <c r="U22" s="3">
         <v>600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>3500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>5300</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1858,77 +1898,80 @@
       <c r="AC22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-10700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>21000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>15700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>12900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-15800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>13700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>23700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>8400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>5400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-12900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4900</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1941,77 +1984,80 @@
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-2300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>11900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-12100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-3500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-5700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-500</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2024,8 +2070,11 @@
       <c r="AC24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2107,77 +2156,80 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-8500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>17000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>12900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>6000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>11200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>19200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>8900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-4700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-14300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>5400</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2190,77 +2242,80 @@
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-8500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>17000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>12900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>11200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>19200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>5500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>8900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-14300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>5400</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2273,8 +2328,11 @@
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2356,8 +2414,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2439,8 +2500,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2522,8 +2586,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2605,13 +2672,16 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
         <v>100</v>
@@ -2623,59 +2693,59 @@
         <v>100</v>
       </c>
       <c r="H32" s="3">
+        <v>100</v>
+      </c>
+      <c r="I32" s="3">
         <v>1100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-300</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>600</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2688,77 +2758,80 @@
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-8500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>17000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>12900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>6000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>11200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>19200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>8900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-4700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-14300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5400</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2771,8 +2844,11 @@
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2854,77 +2930,80 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-8500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>17000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>12900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>6000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>11200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>19200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>8900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-4700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-14300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5400</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2937,82 +3016,85 @@
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3025,8 +3107,11 @@
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3056,8 +3141,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3087,71 +3173,72 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E41" s="3">
         <v>40100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>45600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>55000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>42300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>63300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>73800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>73300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>77600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>78000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>105200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>95600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>72200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>59800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>53300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>20900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>16400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>22600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>21000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>19500</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3170,8 +3257,11 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3179,13 +3269,13 @@
         <v>400</v>
       </c>
       <c r="E42" s="3">
+        <v>400</v>
+      </c>
+      <c r="F42" s="3">
         <v>500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>400</v>
-      </c>
-      <c r="G42" s="3">
-        <v>800</v>
       </c>
       <c r="H42" s="3">
         <v>800</v>
@@ -3194,17 +3284,17 @@
         <v>800</v>
       </c>
       <c r="J42" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="K42" s="3">
         <v>1000</v>
       </c>
       <c r="L42" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M42" s="3">
         <v>800</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -3253,71 +3343,74 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E43" s="3">
         <v>8800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>19200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>22500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>12800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>28200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>23800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>15300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>16200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>21200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>32900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>14500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>18200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>15300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>10100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>8900</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3336,8 +3429,11 @@
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3368,8 +3464,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3419,8 +3515,11 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3451,39 +3550,39 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>3500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5800</v>
-      </c>
-      <c r="P45" s="3">
-        <v>3700</v>
       </c>
       <c r="Q45" s="3">
         <v>3700</v>
       </c>
       <c r="R45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="S45" s="3">
         <v>3200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>6100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4600</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3502,71 +3601,74 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>42600</v>
+      </c>
+      <c r="E46" s="3">
         <v>52200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>57200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>79300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>71100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>76600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>90200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>107400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>108300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>96600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>124900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>121700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>111000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>78000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>75200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>39400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>31000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>31400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>32500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>33000</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3585,55 +3687,58 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E47" s="3">
         <v>200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>600</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R47" s="3">
-        <v>7100</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S47" s="3">
         <v>7100</v>
@@ -3641,8 +3746,8 @@
       <c r="T47" s="3">
         <v>7100</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
+      <c r="U47" s="3">
+        <v>7100</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
@@ -3659,8 +3764,8 @@
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA47" s="3">
-        <v>0</v>
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB47" s="3">
         <v>0</v>
@@ -3668,71 +3773,74 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>301300</v>
+      </c>
+      <c r="E48" s="3">
         <v>266900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>259500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>254000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>248700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>235700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>218600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>210000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>199400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>188500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>180800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>174200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>176400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>178500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>181200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>179700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>184700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>182800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>187600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>190500</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3751,71 +3859,74 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E49" s="3">
         <v>17900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>18100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>18500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>17900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>18200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>18400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>15000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>15300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>15500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>15800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>15900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>13700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>13900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>14100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>15000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>13400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>13700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>14000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>14500</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3834,8 +3945,11 @@
       <c r="AC49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3917,8 +4031,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4000,71 +4117,74 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E52" s="3">
         <v>15500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>12000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>11700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>10300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>10100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>10900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>12200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>13200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>16600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>16000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>18500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>15400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>18200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>19200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>13600</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4083,8 +4203,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4166,71 +4289,74 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>382500</v>
+      </c>
+      <c r="E54" s="3">
         <v>354200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>349000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>374100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>362000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>354700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>350200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>345600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>336300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>324300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>332300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>323900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>314300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>287000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>286500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>259700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>251600</v>
-      </c>
-      <c r="T54" s="3">
-        <v>253400</v>
       </c>
       <c r="U54" s="3">
         <v>253400</v>
       </c>
       <c r="V54" s="3">
+        <v>253400</v>
+      </c>
+      <c r="W54" s="3">
         <v>251500</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4249,8 +4375,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4280,8 +4409,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4311,71 +4441,72 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E57" s="3">
         <v>16400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>12300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4400</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4394,40 +4525,43 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E58" s="3">
         <v>14300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>14000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>11400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>10400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>9300</v>
-      </c>
-      <c r="I58" s="3">
-        <v>8300</v>
       </c>
       <c r="J58" s="3">
         <v>8300</v>
       </c>
       <c r="K58" s="3">
-        <v>8400</v>
+        <v>8300</v>
       </c>
       <c r="L58" s="3">
         <v>8400</v>
       </c>
       <c r="M58" s="3">
-        <v>7900</v>
+        <v>8400</v>
       </c>
       <c r="N58" s="3">
         <v>7900</v>
@@ -4436,29 +4570,29 @@
         <v>7900</v>
       </c>
       <c r="P58" s="3">
-        <v>7800</v>
+        <v>7900</v>
       </c>
       <c r="Q58" s="3">
         <v>7800</v>
       </c>
       <c r="R58" s="3">
-        <v>9600</v>
+        <v>7800</v>
       </c>
       <c r="S58" s="3">
         <v>9600</v>
       </c>
       <c r="T58" s="3">
-        <v>9500</v>
+        <v>9600</v>
       </c>
       <c r="U58" s="3">
         <v>9500</v>
       </c>
       <c r="V58" s="3">
+        <v>9500</v>
+      </c>
+      <c r="W58" s="3">
         <v>9400</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4477,71 +4611,74 @@
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3">
         <v>600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1600</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3">
         <v>300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>600</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
         <v>900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>15900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>19100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>19900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>13200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>13600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>14200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>13000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>12600</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4560,71 +4697,74 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>55500</v>
+      </c>
+      <c r="E60" s="3">
         <v>41000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>33500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>38900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>42900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>33800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>29400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>30200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>35000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>23900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>28400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>30300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>32300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>26100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>24600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>29000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>29100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>26000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>28500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>26400</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4643,71 +4783,74 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>62100</v>
+      </c>
+      <c r="E61" s="3">
         <v>45600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>48900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>50600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>53700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>56700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>59800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>61800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>63800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>65900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>63500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>65500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>67500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>69400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>71400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>49000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>51400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>53900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>56300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>58700</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4726,71 +4869,74 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E62" s="3">
         <v>9500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>10300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>13300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>9300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>9500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>8000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>8200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>8500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>8700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>9000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>9600</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4809,8 +4955,11 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4892,8 +5041,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4975,8 +5127,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5058,71 +5213,74 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>127800</v>
+      </c>
+      <c r="E66" s="3">
         <v>96000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>91600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>98800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>106700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>100400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>100000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>102400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>108500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>99300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>105200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>105100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>109400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>103600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>104200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>85700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>89000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>88600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>93700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>94700</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5141,8 +5299,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5172,8 +5333,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5255,8 +5417,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5338,8 +5503,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5421,8 +5589,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5504,65 +5675,68 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>49400</v>
+      </c>
+      <c r="E72" s="3">
         <v>54900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>55300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>63800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>46800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>47500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>45600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>40800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>27900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>26900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>30700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>24700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>13500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-4500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-10000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-18900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-14300</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5578,8 +5752,8 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA72" s="3">
-        <v>0</v>
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB72" s="3">
         <v>0</v>
@@ -5587,8 +5761,11 @@
       <c r="AC72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5670,8 +5847,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5753,8 +5933,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5836,71 +6019,74 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>254700</v>
+      </c>
+      <c r="E76" s="3">
         <v>258200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>257400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>275300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>255300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>254300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>250200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>243200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>227800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>225100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>227100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>218800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>204900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>183400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>182300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>174100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>162600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>164700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>159600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>156900</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5919,8 +6105,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6002,82 +6191,85 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6090,77 +6282,80 @@
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-8500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>17000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>12900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>6000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>11200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>19200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>8900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-4700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-14300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5400</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6173,8 +6368,11 @@
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6204,31 +6402,32 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E83" s="3">
         <v>5100</v>
-      </c>
-      <c r="E83" s="3">
-        <v>5000</v>
       </c>
       <c r="F83" s="3">
         <v>5000</v>
       </c>
       <c r="G83" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H83" s="3">
         <v>4900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4900</v>
-      </c>
-      <c r="J83" s="3">
-        <v>4800</v>
       </c>
       <c r="K83" s="3">
         <v>4800</v>
@@ -6237,22 +6436,22 @@
         <v>4800</v>
       </c>
       <c r="M83" s="3">
-        <v>5200</v>
+        <v>4800</v>
       </c>
       <c r="N83" s="3">
         <v>5200</v>
       </c>
       <c r="O83" s="3">
+        <v>5200</v>
+      </c>
+      <c r="P83" s="3">
         <v>5100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5800</v>
-      </c>
-      <c r="R83" s="3">
-        <v>5700</v>
       </c>
       <c r="S83" s="3">
         <v>5700</v>
@@ -6261,20 +6460,20 @@
         <v>5700</v>
       </c>
       <c r="U83" s="3">
+        <v>5700</v>
+      </c>
+      <c r="V83" s="3">
         <v>6000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>16100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>5000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>14800</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6287,8 +6486,11 @@
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6370,8 +6572,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6453,8 +6658,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6536,8 +6744,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6619,8 +6830,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6702,77 +6916,80 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E89" s="3">
         <v>9100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>28600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>14300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>21500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>13500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>17900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-11800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>21300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>33000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>17200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>9600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>21600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>10100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>7800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>6700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>21900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>6200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>21700</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6785,8 +7002,11 @@
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6816,77 +7036,78 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-33700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-11600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-9800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-12600</v>
       </c>
-      <c r="G91" s="3">
-        <v>-18800</v>
-      </c>
       <c r="H91" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="I91" s="3">
         <v>-22800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-17700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-15800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-16300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-13300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-9500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-14200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-11600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-33600</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6899,8 +7120,11 @@
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6982,8 +7206,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7065,77 +7292,80 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-35800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-11600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-8100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-12600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-18800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-22800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-17700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-15800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-16300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-13300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-7500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-8100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-7300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-13100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-12500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-32100</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7148,8 +7378,11 @@
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7179,8 +7412,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7211,8 +7445,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7262,8 +7496,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7345,8 +7582,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7428,8 +7668,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7511,31 +7754,34 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3300</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-2000</v>
       </c>
       <c r="K100" s="3">
         <v>-2000</v>
@@ -7544,44 +7790,44 @@
         <v>-2000</v>
       </c>
       <c r="M100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="N100" s="3">
         <v>-2200</v>
-      </c>
-      <c r="N100" s="3">
-        <v>-2000</v>
       </c>
       <c r="O100" s="3">
         <v>-2000</v>
       </c>
       <c r="P100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>18500</v>
-      </c>
-      <c r="R100" s="3">
-        <v>-2500</v>
       </c>
       <c r="S100" s="3">
         <v>-2500</v>
       </c>
       <c r="T100" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="U100" s="3">
         <v>-4900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>13500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-41000</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7594,8 +7840,11 @@
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7626,8 +7875,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -7677,77 +7926,80 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-9400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>12700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-21000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-10500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-27100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>9600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>23500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>12400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>6500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>32000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>4700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-6300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>9900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>6800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-51400</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7758,6 +8010,9 @@
         <v>3</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MNTK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MNTK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="92">
   <si>
     <t>MNTK</t>
   </si>
@@ -656,118 +656,118 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
@@ -780,83 +780,86 @@
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>43400</v>
+      </c>
+      <c r="E8" s="3">
         <v>45300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>45100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>42600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>27700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>65900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>43300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>38800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>46800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>55700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>53300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>19200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>49600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>55900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>67900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>32200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>45300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>39700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>31700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>31400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>24800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>75600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>22000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>83700</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
@@ -869,83 +872,86 @@
       <c r="AE8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>28500</v>
+      </c>
+      <c r="E9" s="3">
         <v>25900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>31000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>25100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>22900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>26600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>27700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>21000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>25400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>25700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>25400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>18100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>24700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>26300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>30000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>20400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>22400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>19800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>19200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>16800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>16100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>45700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>12200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>46500</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
@@ -958,83 +964,86 @@
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E10" s="3">
         <v>19300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>14100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>17500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>39300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>15600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>17800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>21400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>30000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>27800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>24900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>29600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>37900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>11800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>22900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>19900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>12500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>14600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>8700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>29900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>9800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>37200</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1047,8 +1056,11 @@
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1080,8 +1092,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1169,8 +1182,11 @@
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1258,83 +1274,86 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3600</v>
       </c>
-      <c r="G14" s="3">
-        <v>-2600</v>
-      </c>
       <c r="H14" s="3">
+        <v>400</v>
+      </c>
+      <c r="I14" s="3">
         <v>500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2300</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>100</v>
       </c>
       <c r="R14" s="3">
         <v>100</v>
       </c>
       <c r="S14" s="3">
+        <v>100</v>
+      </c>
+      <c r="T14" s="3">
         <v>700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>200</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>600</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1600</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1347,8 +1366,11 @@
       <c r="AE14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1356,34 +1378,34 @@
         <v>8300</v>
       </c>
       <c r="E15" s="3">
+        <v>8300</v>
+      </c>
+      <c r="F15" s="3">
         <v>7000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>6300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>6200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>6000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5800</v>
-      </c>
-      <c r="J15" s="3">
-        <v>5400</v>
       </c>
       <c r="K15" s="3">
         <v>5400</v>
       </c>
       <c r="L15" s="3">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="M15" s="3">
         <v>5300</v>
       </c>
       <c r="N15" s="3">
-        <v>5200</v>
+        <v>5300</v>
       </c>
       <c r="O15" s="3">
         <v>5200</v>
@@ -1392,16 +1414,16 @@
         <v>5200</v>
       </c>
       <c r="Q15" s="3">
+        <v>5200</v>
+      </c>
+      <c r="R15" s="3">
         <v>5100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>5200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>5800</v>
-      </c>
-      <c r="T15" s="3">
-        <v>5700</v>
       </c>
       <c r="U15" s="3">
         <v>5700</v>
@@ -1410,20 +1432,20 @@
         <v>5700</v>
       </c>
       <c r="W15" s="3">
+        <v>5700</v>
+      </c>
+      <c r="X15" s="3">
         <v>6000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>16100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>5000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>14800</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1436,8 +1458,11 @@
       <c r="AE15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1466,83 +1491,84 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>44300</v>
+      </c>
+      <c r="E17" s="3">
         <v>40800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>47100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>38600</v>
       </c>
-      <c r="G17" s="3">
-        <v>40100</v>
-      </c>
       <c r="H17" s="3">
+        <v>37200</v>
+      </c>
+      <c r="I17" s="3">
         <v>42700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>42300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>35800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>39100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>38900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>39400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>32800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>41000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>42200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>43900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>33800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>36100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>33000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>32200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>43700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>26900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>69900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>21100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>73600</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1555,83 +1581,86 @@
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E18" s="3">
         <v>4500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4000</v>
       </c>
-      <c r="G18" s="3">
-        <v>-12400</v>
-      </c>
       <c r="H18" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="I18" s="3">
         <v>23200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>7700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>16800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>13800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-13600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>8600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>13700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>24000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>9200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>6700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-12300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>5700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>10100</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1644,8 +1673,11 @@
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1677,19 +1709,20 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-1500</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
         <v>-100</v>
@@ -1701,59 +1734,59 @@
         <v>-100</v>
       </c>
       <c r="J20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K20" s="3">
         <v>-1100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>300</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-600</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>100</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1766,83 +1799,86 @@
       <c r="AE20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E21" s="3">
         <v>12800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>10300</v>
       </c>
-      <c r="G21" s="3">
-        <v>-6100</v>
-      </c>
       <c r="H21" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="I21" s="3">
         <v>29400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>9500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>13200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>22400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>19200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-8400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>13900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>18900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>29100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>15000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>11800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-6500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>3600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>21500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>5800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>25000</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1855,83 +1891,86 @@
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E22" s="3">
         <v>1100</v>
-      </c>
-      <c r="E22" s="3">
-        <v>1200</v>
       </c>
       <c r="F22" s="3">
         <v>1200</v>
       </c>
       <c r="G22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H22" s="3">
         <v>1000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1500</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
         <v>300</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
       <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
         <v>900</v>
-      </c>
-      <c r="T22" s="3">
-        <v>700</v>
       </c>
       <c r="U22" s="3">
         <v>700</v>
       </c>
       <c r="V22" s="3">
+        <v>700</v>
+      </c>
+      <c r="W22" s="3">
         <v>600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>3500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>5300</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1944,83 +1983,86 @@
       <c r="AE22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E23" s="3">
         <v>3400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>21000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>15700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>12900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-15800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>13700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>23700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>8400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>5400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-12900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-3200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4900</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
@@ -2033,83 +2075,86 @@
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-2300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>11900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-12100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>4600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-3500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-5700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-500</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2122,8 +2167,11 @@
       <c r="AE24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2211,83 +2259,86 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E26" s="3">
         <v>5200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-8500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>17000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>12900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>11200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>19200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>5500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>8900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-4700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-14300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>5400</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2300,83 +2351,86 @@
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E27" s="3">
         <v>5200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>17000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>12900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>11200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>19200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>8900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-4700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-14300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>5400</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2389,8 +2443,11 @@
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2478,8 +2535,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2567,8 +2627,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2656,8 +2719,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2745,19 +2811,22 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
         <v>100</v>
@@ -2769,59 +2838,59 @@
         <v>100</v>
       </c>
       <c r="J32" s="3">
+        <v>100</v>
+      </c>
+      <c r="K32" s="3">
         <v>1100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-300</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>600</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-100</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2834,83 +2903,86 @@
       <c r="AE32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E33" s="3">
         <v>5200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>17000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>12900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>11200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>19200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>8900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-4700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-14300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>5400</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2923,8 +2995,11 @@
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3012,83 +3087,86 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E35" s="3">
         <v>5200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>17000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>12900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>11200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>19200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>8900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-4700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-14300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>5400</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3101,88 +3179,91 @@
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3195,8 +3276,11 @@
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3228,8 +3312,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3261,77 +3346,78 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E41" s="3">
         <v>6800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>29100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>40100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>45600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>55000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>42300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>63300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>73800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>73300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>77600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>78000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>105200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>95600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>72200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>59800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>53300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>20900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>16400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>22600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>21000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>19500</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3350,28 +3436,31 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>200</v>
+      </c>
+      <c r="E42" s="3">
         <v>300</v>
-      </c>
-      <c r="E42" s="3">
-        <v>400</v>
       </c>
       <c r="F42" s="3">
         <v>400</v>
       </c>
       <c r="G42" s="3">
+        <v>400</v>
+      </c>
+      <c r="H42" s="3">
         <v>500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>400</v>
-      </c>
-      <c r="I42" s="3">
-        <v>800</v>
       </c>
       <c r="J42" s="3">
         <v>800</v>
@@ -3380,17 +3469,17 @@
         <v>800</v>
       </c>
       <c r="L42" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="M42" s="3">
         <v>1000</v>
       </c>
       <c r="N42" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O42" s="3">
         <v>800</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -3439,77 +3528,80 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E43" s="3">
         <v>6700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>19200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>22500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>9800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>12800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>28200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>23800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>15300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>16200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>21200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>32900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>14500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>18200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>15300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>10100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>8900</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3528,8 +3620,11 @@
       <c r="AE43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3566,8 +3661,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3617,8 +3712,11 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3655,39 +3753,39 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>3500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5800</v>
-      </c>
-      <c r="R45" s="3">
-        <v>3700</v>
       </c>
       <c r="S45" s="3">
         <v>3700</v>
       </c>
       <c r="T45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="U45" s="3">
         <v>3200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>6100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>4600</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3706,77 +3804,80 @@
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>37200</v>
+      </c>
+      <c r="E46" s="3">
         <v>18000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>42600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>52200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>57200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>79300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>71100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>76600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>90200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>107400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>108300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>96600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>124900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>121700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>111000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>78000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>75200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>39400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>31000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>31400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>32500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>33000</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3795,61 +3896,64 @@
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E47" s="3">
         <v>4200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>600</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
-      </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T47" s="3">
-        <v>7100</v>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U47" s="3">
         <v>7100</v>
@@ -3857,8 +3961,8 @@
       <c r="V47" s="3">
         <v>7100</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
+      <c r="W47" s="3">
+        <v>7100</v>
       </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
@@ -3875,8 +3979,8 @@
       <c r="AB47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC47" s="3">
-        <v>0</v>
+      <c r="AC47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD47" s="3">
         <v>0</v>
@@ -3884,77 +3988,80 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>350500</v>
+      </c>
+      <c r="E48" s="3">
         <v>321800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>301300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>266900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>259500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>254000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>248700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>235700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>218600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>210000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>199400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>188500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>180800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>174200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>176400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>178500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>181200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>179700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>184700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>182800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>187600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>190500</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3973,77 +4080,80 @@
       <c r="AE48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E49" s="3">
         <v>19900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>20100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>17900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>18100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>18500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>17900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>18200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>18400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>15000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>15300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>15500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>15800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>15900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>13700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>13900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>14100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>15000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>13400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>13700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>14000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>14500</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4062,8 +4172,11 @@
       <c r="AE49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4151,8 +4264,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4240,77 +4356,80 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E52" s="3">
         <v>17900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>16200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>15500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>12600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>12000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>11700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>8600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>10900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>12200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>13200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>16600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>16000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>18500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>15400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>18200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>19200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>13600</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4329,8 +4448,11 @@
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4418,77 +4540,80 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>435500</v>
+      </c>
+      <c r="E54" s="3">
         <v>383300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>382500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>354200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>349000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>374100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>362000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>354700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>350200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>345600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>336300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>324300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>332300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>323900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>314300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>287000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>286500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>259700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>251600</v>
-      </c>
-      <c r="V54" s="3">
-        <v>253400</v>
       </c>
       <c r="W54" s="3">
         <v>253400</v>
       </c>
       <c r="X54" s="3">
+        <v>253400</v>
+      </c>
+      <c r="Y54" s="3">
         <v>251500</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4507,8 +4632,11 @@
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4540,8 +4668,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4573,77 +4702,78 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E57" s="3">
         <v>25400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>27200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>16400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>11900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>12300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>6000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4400</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4662,46 +4792,49 @@
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>14400</v>
+        <v>6100</v>
       </c>
       <c r="E58" s="3">
         <v>14400</v>
       </c>
       <c r="F58" s="3">
+        <v>14400</v>
+      </c>
+      <c r="G58" s="3">
         <v>14300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>14000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>11400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>9300</v>
-      </c>
-      <c r="K58" s="3">
-        <v>8300</v>
       </c>
       <c r="L58" s="3">
         <v>8300</v>
       </c>
       <c r="M58" s="3">
-        <v>8400</v>
+        <v>8300</v>
       </c>
       <c r="N58" s="3">
         <v>8400</v>
       </c>
       <c r="O58" s="3">
-        <v>7900</v>
+        <v>8400</v>
       </c>
       <c r="P58" s="3">
         <v>7900</v>
@@ -4710,29 +4843,29 @@
         <v>7900</v>
       </c>
       <c r="R58" s="3">
-        <v>7800</v>
+        <v>7900</v>
       </c>
       <c r="S58" s="3">
         <v>7800</v>
       </c>
       <c r="T58" s="3">
-        <v>9600</v>
+        <v>7800</v>
       </c>
       <c r="U58" s="3">
         <v>9600</v>
       </c>
       <c r="V58" s="3">
-        <v>9500</v>
+        <v>9600</v>
       </c>
       <c r="W58" s="3">
         <v>9500</v>
       </c>
       <c r="X58" s="3">
+        <v>9500</v>
+      </c>
+      <c r="Y58" s="3">
         <v>9400</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4751,8 +4884,11 @@
       <c r="AE58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4765,63 +4901,63 @@
       <c r="F59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3">
         <v>600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1600</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3">
         <v>300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>600</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N59" s="3">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3">
         <v>900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>15900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>19100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>19900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>13200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>11800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>13600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>14200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>11000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>13000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>12600</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4840,77 +4976,80 @@
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E60" s="3">
         <v>53900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>55500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>41000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>33500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>38900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>42900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>33800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>29400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>30200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>35000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>23900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>28400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>30300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>32300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>26100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>24600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>29000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>29100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>26000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>28500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>26400</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4929,77 +5068,80 @@
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>131900</v>
+      </c>
+      <c r="E61" s="3">
         <v>58600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>62100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>45600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>48900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>50600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>53700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>56700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>59800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>61800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>63800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>65900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>63500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>65500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>67500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>69400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>71400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>49000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>51400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>53900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>56300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>58700</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -5018,77 +5160,80 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E62" s="3">
         <v>10100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>9100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>10300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>9700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>9600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>13300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>9300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>9500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>8000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>8200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>8500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>8700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>9000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>9600</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5107,8 +5252,11 @@
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5196,8 +5344,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5285,8 +5436,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5374,77 +5528,80 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>172300</v>
+      </c>
+      <c r="E66" s="3">
         <v>122600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>127800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>96000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>91600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>98800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>106700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>100400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>100000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>102400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>108500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>99300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>105200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>105100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>109400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>103600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>104200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>85700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>89000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>88600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>93700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>94700</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5463,8 +5620,11 @@
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5496,8 +5656,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5585,8 +5746,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5674,8 +5838,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5763,8 +5930,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5852,71 +6022,74 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>57100</v>
+      </c>
+      <c r="E72" s="3">
         <v>54600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>49400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>54900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>55300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>63800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>46800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>47500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>45600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>40800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>27900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>26900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>30700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>24700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>13500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-5600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-4500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-10000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-18900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-14300</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5932,8 +6105,8 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC72" s="3">
-        <v>0</v>
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD72" s="3">
         <v>0</v>
@@ -5941,8 +6114,11 @@
       <c r="AE72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6030,8 +6206,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6119,8 +6298,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6208,77 +6390,80 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>263100</v>
+      </c>
+      <c r="E76" s="3">
         <v>260700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>254700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>258200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>257400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>275300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>255300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>254300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>250200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>243200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>227800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>225100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>227100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>218800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>204900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>183400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>182300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>174100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>162600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>164700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>159600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>156900</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6297,8 +6482,11 @@
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6386,88 +6574,91 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6480,83 +6671,86 @@
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E81" s="3">
         <v>5200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>17000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>12900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>11200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>19200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>8900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-4700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-14300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>5400</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6569,8 +6763,11 @@
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6602,37 +6799,38 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E83" s="3">
         <v>5700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5100</v>
-      </c>
-      <c r="G83" s="3">
-        <v>5000</v>
       </c>
       <c r="H83" s="3">
         <v>5000</v>
       </c>
       <c r="I83" s="3">
+        <v>5000</v>
+      </c>
+      <c r="J83" s="3">
         <v>4900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4900</v>
-      </c>
-      <c r="L83" s="3">
-        <v>4800</v>
       </c>
       <c r="M83" s="3">
         <v>4800</v>
@@ -6641,22 +6839,22 @@
         <v>4800</v>
       </c>
       <c r="O83" s="3">
-        <v>5200</v>
+        <v>4800</v>
       </c>
       <c r="P83" s="3">
         <v>5200</v>
       </c>
       <c r="Q83" s="3">
+        <v>5200</v>
+      </c>
+      <c r="R83" s="3">
         <v>5100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>5200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>5800</v>
-      </c>
-      <c r="T83" s="3">
-        <v>5700</v>
       </c>
       <c r="U83" s="3">
         <v>5700</v>
@@ -6665,20 +6863,20 @@
         <v>5700</v>
       </c>
       <c r="W83" s="3">
+        <v>5700</v>
+      </c>
+      <c r="X83" s="3">
         <v>6000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>16100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>5000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>14800</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6691,8 +6889,11 @@
       <c r="AE83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6780,8 +6981,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6869,8 +7073,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6958,8 +7165,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7047,8 +7257,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7136,83 +7349,86 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>300</v>
+      </c>
+      <c r="E89" s="3">
         <v>12700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>8200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>9100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>28600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>14300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>21500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>13500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>17900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-11800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>21300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>33000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>17200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>9600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>21600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>10100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>7800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>6700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>21900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>6200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>21700</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7225,8 +7441,11 @@
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7258,83 +7477,84 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-41400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-29800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-33700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-11600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-12600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-18800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-22000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-17700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-15800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-16300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-9500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-14200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-11600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-33600</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7347,8 +7567,11 @@
       <c r="AE91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7436,8 +7659,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7525,83 +7751,86 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-41300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-31800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-35800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-11600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-8100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-12600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-18800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-22800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-17700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-15800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-16300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-13300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-7500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-8100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-7300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-13100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-12500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-32100</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7614,8 +7843,11 @@
       <c r="AE94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7647,8 +7879,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7685,8 +7918,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7736,8 +7969,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7825,8 +8061,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7914,8 +8153,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8003,37 +8245,40 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>57900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>16600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3300</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-2000</v>
       </c>
       <c r="M100" s="3">
         <v>-2000</v>
@@ -8042,44 +8287,44 @@
         <v>-2000</v>
       </c>
       <c r="O100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="P100" s="3">
         <v>-2200</v>
-      </c>
-      <c r="P100" s="3">
-        <v>-2000</v>
       </c>
       <c r="Q100" s="3">
         <v>-2000</v>
       </c>
       <c r="R100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="S100" s="3">
         <v>-2100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>18500</v>
-      </c>
-      <c r="T100" s="3">
-        <v>-2500</v>
       </c>
       <c r="U100" s="3">
         <v>-2500</v>
       </c>
       <c r="V100" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="W100" s="3">
         <v>-4900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>13500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-41000</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8092,8 +8337,11 @@
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8130,8 +8378,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -8181,83 +8429,86 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-22300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-11000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-9400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>12700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-21000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-10500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-27100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>9600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>23500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>12400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>6500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>32000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>4700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-6300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>9900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>6800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-51400</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8268,6 +8519,9 @@
         <v>3</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MNTK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MNTK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="92">
   <si>
     <t>MNTK</t>
   </si>
@@ -656,121 +656,122 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43830</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43738</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
@@ -783,86 +784,89 @@
       <c r="AF7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>46400</v>
+      </c>
+      <c r="E8" s="3">
         <v>43400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>45300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>45100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>42600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>27700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>65900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>43300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>38800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>46800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>55700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>53300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>19200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>49600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>55900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>67900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>32200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>45300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>39700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>31700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>31400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>24800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>75600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>22000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>83700</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
@@ -875,86 +879,89 @@
       <c r="AF8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E9" s="3">
         <v>28500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>25900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>31000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>25100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>22900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>26600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>27700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>21000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>25400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>25700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>25400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>18100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>24700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>26300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>30000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>20400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>22400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>19800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>19200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>16800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>16100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>45700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>12200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>46500</v>
       </c>
-      <c r="AB9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
@@ -967,86 +974,89 @@
       <c r="AF9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E10" s="3">
         <v>14900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>19300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>14100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>17500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>39300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>15600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>17800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>21400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>30000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>27800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>24900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>29600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>37900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>11800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>22900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>19900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>12500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>14600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>8700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>29900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>9800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>37200</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1059,8 +1069,11 @@
       <c r="AF10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1093,8 +1106,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1185,8 +1199,11 @@
       <c r="AF12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1277,86 +1294,89 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E14" s="3">
         <v>800</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>400</v>
       </c>
-      <c r="G14" s="3">
-        <v>3600</v>
-      </c>
       <c r="H14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I14" s="3">
         <v>400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2300</v>
-      </c>
-      <c r="R14" s="3">
-        <v>100</v>
       </c>
       <c r="S14" s="3">
         <v>100</v>
       </c>
       <c r="T14" s="3">
+        <v>100</v>
+      </c>
+      <c r="U14" s="3">
         <v>700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>200</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>600</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1600</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1369,46 +1389,49 @@
       <c r="AF14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>8300</v>
+        <v>8400</v>
       </c>
       <c r="E15" s="3">
         <v>8300</v>
       </c>
       <c r="F15" s="3">
+        <v>8300</v>
+      </c>
+      <c r="G15" s="3">
         <v>7000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>6300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>6200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>6000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5800</v>
-      </c>
-      <c r="K15" s="3">
-        <v>5400</v>
       </c>
       <c r="L15" s="3">
         <v>5400</v>
       </c>
       <c r="M15" s="3">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="N15" s="3">
         <v>5300</v>
       </c>
       <c r="O15" s="3">
-        <v>5200</v>
+        <v>5300</v>
       </c>
       <c r="P15" s="3">
         <v>5200</v>
@@ -1417,16 +1440,16 @@
         <v>5200</v>
       </c>
       <c r="R15" s="3">
+        <v>5200</v>
+      </c>
+      <c r="S15" s="3">
         <v>5100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>5200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>5800</v>
-      </c>
-      <c r="U15" s="3">
-        <v>5700</v>
       </c>
       <c r="V15" s="3">
         <v>5700</v>
@@ -1435,20 +1458,20 @@
         <v>5700</v>
       </c>
       <c r="X15" s="3">
+        <v>5700</v>
+      </c>
+      <c r="Y15" s="3">
         <v>6000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>16100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>5000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>14800</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1461,8 +1484,11 @@
       <c r="AF15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1492,86 +1518,87 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>47600</v>
+      </c>
+      <c r="E17" s="3">
         <v>44300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>40800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>47100</v>
       </c>
-      <c r="G17" s="3">
-        <v>38600</v>
-      </c>
       <c r="H17" s="3">
+        <v>40100</v>
+      </c>
+      <c r="I17" s="3">
         <v>37200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>42700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>42300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>35800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>39100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>38900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>39400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>32800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>41000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>42200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>43900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>33800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>36100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>33000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>32200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>43700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>26900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>69900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>21100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>73600</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1584,86 +1611,89 @@
       <c r="AF17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2000</v>
       </c>
-      <c r="G18" s="3">
-        <v>4000</v>
-      </c>
       <c r="H18" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I18" s="3">
         <v>-9500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>23200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>7700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>16800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>13800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-13600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>8600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>13700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>24000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>9200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>6700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-12300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>5700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>10100</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1676,8 +1706,11 @@
       <c r="AF18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1710,22 +1743,23 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1500</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
         <v>-100</v>
@@ -1737,59 +1771,59 @@
         <v>-100</v>
       </c>
       <c r="K20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L20" s="3">
         <v>-1100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>300</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-600</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>100</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1802,86 +1836,89 @@
       <c r="AF20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E21" s="3">
         <v>8900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>12800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5000</v>
       </c>
-      <c r="G21" s="3">
-        <v>10300</v>
-      </c>
       <c r="H21" s="3">
+        <v>8800</v>
+      </c>
+      <c r="I21" s="3">
         <v>-3200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>29400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>6900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>9500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>13200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>22400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>19200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-8400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>13900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>18900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>29100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>15000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>11800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>5100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-6500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>3600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>21500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>5800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>25000</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1894,8 +1931,11 @@
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1903,77 +1943,77 @@
         <v>1300</v>
       </c>
       <c r="E22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F22" s="3">
         <v>1100</v>
-      </c>
-      <c r="F22" s="3">
-        <v>1200</v>
       </c>
       <c r="G22" s="3">
         <v>1200</v>
       </c>
       <c r="H22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I22" s="3">
         <v>1000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1500</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
         <v>300</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
       <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
         <v>900</v>
-      </c>
-      <c r="U22" s="3">
-        <v>700</v>
       </c>
       <c r="V22" s="3">
         <v>700</v>
       </c>
       <c r="W22" s="3">
+        <v>700</v>
+      </c>
+      <c r="X22" s="3">
         <v>600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>3500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>5300</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1986,86 +2026,89 @@
       <c r="AF22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-10700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>21000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>15700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>12900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-15800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>13700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>23700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>8400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>5400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-12900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4900</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
@@ -2078,86 +2121,89 @@
       <c r="AF23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E24" s="3">
         <v>-3900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-2300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>11900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-12100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>4600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-3500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>3400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-5700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-500</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2170,8 +2216,11 @@
       <c r="AF24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2262,86 +2311,89 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3">
         <v>2500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-8500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>17000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>12900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>6000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>11200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>19200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>5500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>8900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-4700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-14300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>5400</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2354,86 +2406,89 @@
       <c r="AF26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3">
         <v>2500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>5200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-8500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>17000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>12900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>6000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>11200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>19200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>5500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>8900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-4700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-14300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>5400</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2446,8 +2501,11 @@
       <c r="AF27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2538,8 +2596,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2630,8 +2691,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2722,8 +2786,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2814,22 +2881,25 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E32" s="3">
         <v>1500</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
         <v>100</v>
@@ -2841,59 +2911,59 @@
         <v>100</v>
       </c>
       <c r="K32" s="3">
+        <v>100</v>
+      </c>
+      <c r="L32" s="3">
         <v>1100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-300</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>600</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-100</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2906,86 +2976,89 @@
       <c r="AF32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3">
         <v>2500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>5200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-8500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>17000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>12900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>11200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>19200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>8900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-4700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-14300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>5400</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2998,8 +3071,11 @@
       <c r="AF33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3090,86 +3166,89 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3">
         <v>2500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>5200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-8500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>17000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>12900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>11200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>19200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>8900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-4700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-14300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>5400</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3182,91 +3261,94 @@
       <c r="AF35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43830</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43738</v>
       </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3279,8 +3361,11 @@
       <c r="AF38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3313,8 +3398,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3347,80 +3433,81 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E41" s="3">
         <v>23800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>29100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>40100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>45600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>55000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>42300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>63300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>73800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>73300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>77600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>78000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>105200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>95600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>72200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>59800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>53300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>20900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>16400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>22600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>21000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>19500</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3439,31 +3526,34 @@
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>300</v>
-      </c>
-      <c r="F42" s="3">
-        <v>400</v>
       </c>
       <c r="G42" s="3">
         <v>400</v>
       </c>
       <c r="H42" s="3">
+        <v>400</v>
+      </c>
+      <c r="I42" s="3">
         <v>500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>400</v>
-      </c>
-      <c r="J42" s="3">
-        <v>800</v>
       </c>
       <c r="K42" s="3">
         <v>800</v>
@@ -3472,17 +3562,17 @@
         <v>800</v>
       </c>
       <c r="M42" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="N42" s="3">
         <v>1000</v>
       </c>
       <c r="O42" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P42" s="3">
         <v>800</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -3531,80 +3621,83 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E43" s="3">
         <v>9900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>19200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>22500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>12800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>28200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>23800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>15300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>16200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>21200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>32900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>14500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>18200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>15300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>10100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>8900</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3623,8 +3716,11 @@
       <c r="AF43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3664,8 +3760,8 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3715,8 +3811,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3756,39 +3855,39 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>3500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5800</v>
-      </c>
-      <c r="S45" s="3">
-        <v>3700</v>
       </c>
       <c r="T45" s="3">
         <v>3700</v>
       </c>
       <c r="U45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="V45" s="3">
         <v>3200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>6100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>4600</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3807,80 +3906,83 @@
       <c r="AF45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>35700</v>
+      </c>
+      <c r="E46" s="3">
         <v>37200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>18000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>42600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>52200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>57200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>79300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>71100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>76600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>90200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>107400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>108300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>96600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>124900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>121700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>111000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>78000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>75200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>39400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>31000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>31400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>32500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>33000</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3899,8 +4001,11 @@
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3908,55 +4013,55 @@
         <v>3800</v>
       </c>
       <c r="E47" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F47" s="3">
         <v>4200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>600</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
-      </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U47" s="3">
-        <v>7100</v>
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V47" s="3">
         <v>7100</v>
@@ -3964,8 +4069,8 @@
       <c r="W47" s="3">
         <v>7100</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>3</v>
+      <c r="X47" s="3">
+        <v>7100</v>
       </c>
       <c r="Y47" s="3" t="s">
         <v>3</v>
@@ -3982,8 +4087,8 @@
       <c r="AC47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD47" s="3">
-        <v>0</v>
+      <c r="AD47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE47" s="3">
         <v>0</v>
@@ -3991,80 +4096,83 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>379700</v>
+      </c>
+      <c r="E48" s="3">
         <v>350500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>321800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>301300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>266900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>259500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>254000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>248700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>235700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>218600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>210000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>199400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>188500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>180800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>174200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>176400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>178500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>181200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>179700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>184700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>182800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>187600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>190500</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4083,80 +4191,83 @@
       <c r="AF48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E49" s="3">
         <v>19600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>19900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>20100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>17900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>18100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>18500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>17900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>18200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>18400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>15000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>15300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>15500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>15800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>15900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>13700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>13900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>14100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>15000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>13400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>13700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>14000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>14500</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4175,8 +4286,11 @@
       <c r="AF49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4267,8 +4381,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4359,80 +4476,83 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E52" s="3">
         <v>18800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>17900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>16200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>15500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>12600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>12000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>11600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>11700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>10100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>10900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>12200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>13200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>16600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>16000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>18500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>15400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>18200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>19200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>13600</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4451,8 +4571,11 @@
       <c r="AF52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4543,80 +4666,83 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>467800</v>
+      </c>
+      <c r="E54" s="3">
         <v>435500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>383300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>382500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>354200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>349000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>374100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>362000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>354700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>350200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>345600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>336300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>324300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>332300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>323900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>314300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>287000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>286500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>259700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>251600</v>
-      </c>
-      <c r="W54" s="3">
-        <v>253400</v>
       </c>
       <c r="X54" s="3">
         <v>253400</v>
       </c>
       <c r="Y54" s="3">
+        <v>253400</v>
+      </c>
+      <c r="Z54" s="3">
         <v>251500</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4635,8 +4761,11 @@
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4669,8 +4798,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4703,80 +4833,81 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E57" s="3">
         <v>15600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>25400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>27200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>16400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>10200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>12300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>6000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4400</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4795,49 +4926,52 @@
       <c r="AF57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E58" s="3">
         <v>6100</v>
-      </c>
-      <c r="E58" s="3">
-        <v>14400</v>
       </c>
       <c r="F58" s="3">
         <v>14400</v>
       </c>
       <c r="G58" s="3">
+        <v>14400</v>
+      </c>
+      <c r="H58" s="3">
         <v>14300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>14000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>11400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>9300</v>
-      </c>
-      <c r="L58" s="3">
-        <v>8300</v>
       </c>
       <c r="M58" s="3">
         <v>8300</v>
       </c>
       <c r="N58" s="3">
-        <v>8400</v>
+        <v>8300</v>
       </c>
       <c r="O58" s="3">
         <v>8400</v>
       </c>
       <c r="P58" s="3">
-        <v>7900</v>
+        <v>8400</v>
       </c>
       <c r="Q58" s="3">
         <v>7900</v>
@@ -4846,29 +4980,29 @@
         <v>7900</v>
       </c>
       <c r="S58" s="3">
-        <v>7800</v>
+        <v>7900</v>
       </c>
       <c r="T58" s="3">
         <v>7800</v>
       </c>
       <c r="U58" s="3">
-        <v>9600</v>
+        <v>7800</v>
       </c>
       <c r="V58" s="3">
         <v>9600</v>
       </c>
       <c r="W58" s="3">
-        <v>9500</v>
+        <v>9600</v>
       </c>
       <c r="X58" s="3">
         <v>9500</v>
       </c>
       <c r="Y58" s="3">
+        <v>9500</v>
+      </c>
+      <c r="Z58" s="3">
         <v>9400</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4887,8 +5021,11 @@
       <c r="AF58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4904,63 +5041,63 @@
       <c r="G59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3">
         <v>600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1600</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
         <v>300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>600</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3">
         <v>900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>15900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>19100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>19900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>13200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>13600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>14200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>11000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>13000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>12600</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4979,80 +5116,83 @@
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E60" s="3">
         <v>33400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>53900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>55500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>41000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>33500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>38900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>42900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>33800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>29400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>30200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>35000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>23900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>28400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>30300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>32300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>26100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>24600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>29000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>29100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>26000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>28500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>26400</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5071,80 +5211,83 @@
       <c r="AF60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>154900</v>
+      </c>
+      <c r="E61" s="3">
         <v>131900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>58600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>62100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>45600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>48900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>50600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>53700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>56700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>59800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>61800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>63800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>65900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>63500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>65500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>67500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>69400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>71400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>49000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>51400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>53900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>56300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>58700</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -5163,80 +5306,83 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E62" s="3">
         <v>7000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>10100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>9500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>10000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>10900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>10300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>9700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>9600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>13300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>9300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>9500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>8000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>8200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>8500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>8700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>9000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>9600</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5255,8 +5401,11 @@
       <c r="AF62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5347,8 +5496,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5439,8 +5591,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5531,80 +5686,83 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>204000</v>
+      </c>
+      <c r="E66" s="3">
         <v>172300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>122600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>127800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>96000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>91600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>98800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>106700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>100400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>100000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>102400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>108500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>99300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>105200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>105100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>109400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>103600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>104200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>85700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>89000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>88600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>93700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>94700</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5623,8 +5781,11 @@
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5657,8 +5818,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5749,8 +5911,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5841,8 +6006,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5933,8 +6101,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6025,8 +6196,11 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6034,65 +6208,65 @@
         <v>57100</v>
       </c>
       <c r="E72" s="3">
+        <v>57100</v>
+      </c>
+      <c r="F72" s="3">
         <v>54600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>49400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>54900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>55300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>63800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>46800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>47500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>45600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>40800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>27900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>26900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>30700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>24700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>13500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-5600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-4500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-10000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-18900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-14300</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6108,8 +6282,8 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD72" s="3">
-        <v>0</v>
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE72" s="3">
         <v>0</v>
@@ -6117,8 +6291,11 @@
       <c r="AF72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6209,8 +6386,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6301,8 +6481,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6393,80 +6576,83 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>263800</v>
+      </c>
+      <c r="E76" s="3">
         <v>263100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>260700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>254700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>258200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>257400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>275300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>255300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>254300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>250200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>243200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>227800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>225100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>227100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>218800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>204900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>183400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>182300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>174100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>162600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>164700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>159600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>156900</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6485,8 +6671,11 @@
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6577,91 +6766,94 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43830</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43738</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6674,86 +6866,89 @@
       <c r="AF80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3">
         <v>2500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>5200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-8500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>17000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>12900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>11200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>19200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>8900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-4700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-14300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>5400</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6766,8 +6961,11 @@
       <c r="AF81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6800,8 +6998,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6809,31 +7008,31 @@
         <v>5900</v>
       </c>
       <c r="E83" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F83" s="3">
         <v>5700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5100</v>
-      </c>
-      <c r="H83" s="3">
-        <v>5000</v>
       </c>
       <c r="I83" s="3">
         <v>5000</v>
       </c>
       <c r="J83" s="3">
+        <v>5000</v>
+      </c>
+      <c r="K83" s="3">
         <v>4900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4900</v>
-      </c>
-      <c r="M83" s="3">
-        <v>4800</v>
       </c>
       <c r="N83" s="3">
         <v>4800</v>
@@ -6842,22 +7041,22 @@
         <v>4800</v>
       </c>
       <c r="P83" s="3">
-        <v>5200</v>
+        <v>4800</v>
       </c>
       <c r="Q83" s="3">
         <v>5200</v>
       </c>
       <c r="R83" s="3">
+        <v>5200</v>
+      </c>
+      <c r="S83" s="3">
         <v>5100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>5200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>5800</v>
-      </c>
-      <c r="U83" s="3">
-        <v>5700</v>
       </c>
       <c r="V83" s="3">
         <v>5700</v>
@@ -6866,20 +7065,20 @@
         <v>5700</v>
       </c>
       <c r="X83" s="3">
+        <v>5700</v>
+      </c>
+      <c r="Y83" s="3">
         <v>6000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>16100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>5000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>14800</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6892,8 +7091,11 @@
       <c r="AF83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6984,8 +7186,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7076,8 +7281,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7168,8 +7376,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7260,8 +7471,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7352,86 +7566,89 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E89" s="3">
         <v>300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>12700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>8200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>9100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>28600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>14300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>21500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>13500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>17900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-11800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>21300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>33000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>17200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>9600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>21600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>10100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>7800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>6700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>21900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>6200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>21700</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7444,8 +7661,11 @@
       <c r="AF89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7478,86 +7698,87 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-30900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-41400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-29800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-33700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-11600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-12600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-18800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-22000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-17700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-15800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-16300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-14200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-11600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-33600</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7570,8 +7791,11 @@
       <c r="AF91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7662,8 +7886,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7754,86 +7981,89 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-30800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-41300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-31800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-35800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-11600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-12600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-18800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-22800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-17700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-15800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-16300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-13300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-7500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-8100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-7300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-13100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-12500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-32100</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7846,8 +8076,11 @@
       <c r="AF94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7880,8 +8113,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7921,8 +8155,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7972,8 +8206,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8064,8 +8301,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8156,8 +8396,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8248,40 +8491,43 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E100" s="3">
         <v>57900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>16600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3300</v>
-      </c>
-      <c r="M100" s="3">
-        <v>-2000</v>
       </c>
       <c r="N100" s="3">
         <v>-2000</v>
@@ -8290,44 +8536,44 @@
         <v>-2000</v>
       </c>
       <c r="P100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-2200</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>-2000</v>
       </c>
       <c r="R100" s="3">
         <v>-2000</v>
       </c>
       <c r="S100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="T100" s="3">
         <v>-2100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>18500</v>
-      </c>
-      <c r="U100" s="3">
-        <v>-2500</v>
       </c>
       <c r="V100" s="3">
         <v>-2500</v>
       </c>
       <c r="W100" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="X100" s="3">
         <v>-4900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>13500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-41000</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8340,8 +8586,11 @@
       <c r="AF100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8381,8 +8630,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -8432,86 +8681,89 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E102" s="3">
         <v>17000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-22300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-11000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-9400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>12700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-21000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-10500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-27100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>9600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>23500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>12400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>6500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>32000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>4700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-6300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>9900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>6800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-51400</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8522,6 +8774,9 @@
         <v>3</v>
       </c>
       <c r="AF102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
